--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$69</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2525" uniqueCount="405">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -497,7 +500,7 @@
 </t>
   </si>
   <si>
-    <t>Codes that identify this medication</t>
+    <t>Code des Arzneimittels.</t>
   </si>
   <si>
     <t>A code (or set of codes) that specify this medication, or a textual description if no code is available. Usage note: This could be a standard medication code such as a code from RxNorm, SNOMED CT, IDMP etc. It could also be a national or local formulary code, optionally with translations to other code systems.</t>
@@ -534,7 +537,7 @@
     <t>Medication.status</t>
   </si>
   <si>
-    <t>active | inactive | entered-in-error</t>
+    <t>Keine Verwendung. Entered-in-error führt zu inkonsistenten Zuständen.</t>
   </si>
   <si>
     <t>A code to indicate if the medication is in active use.</t>
@@ -583,7 +586,7 @@
     <t>Medication.form</t>
   </si>
   <si>
-    <t>powder | tablets | capsule +</t>
+    <t>Die Darreichungsform des Arzneimittels.</t>
   </si>
   <si>
     <t>Describes the form of the item.  Powder; tablets; capsule.</t>
@@ -592,10 +595,7 @@
     <t>When Medication is referenced from MedicationRequest, this is the ordered form.  When Medication is referenced within MedicationDispense, this is the dispensed form.  When Medication is referenced within MedicationAdministration, this is administered form.</t>
   </si>
   <si>
-    <t>A coded concept defining the form of a medication.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-form-codes|4.0.1</t>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-medikationdarreichungsform</t>
   </si>
   <si>
     <t>coding.code =  //element(*,DrugCodedType)/FormCode@@ -616,13 +616,237 @@
 </t>
   </si>
   <si>
-    <t>Amount of drug in package</t>
+    <t>Die Gesamtmenge des Arzneimittels in der Verpackung.</t>
   </si>
   <si>
     <t>Specific amount of the drug in the packaged product.  For example, when specifying a product that has the same strength (For example, Insulin glargine 100 unit per mL solution for injection), this attribute provides additional clarification of the package amount (For example, 3 mL, 10mL, etc.).</t>
   </si>
   <si>
     <t>.quantity</t>
+  </si>
+  <si>
+    <t>Medication.amount.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Medication.amount.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Medication.amount.numerator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>Numerator value</t>
+  </si>
+  <si>
+    <t>The value of the numerator.</t>
+  </si>
+  <si>
+    <t>Ratio.numerator</t>
+  </si>
+  <si>
+    <t>.numerator</t>
+  </si>
+  <si>
+    <t>Medication.amount.numerator.id</t>
+  </si>
+  <si>
+    <t>Medication.amount.numerator.extension</t>
+  </si>
+  <si>
+    <t>Medication.amount.numerator.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Numerical value (with implicit precision)</t>
+  </si>
+  <si>
+    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
+  </si>
+  <si>
+    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
+  </si>
+  <si>
+    <t>Precision is handled implicitly in almost all cases of measurement.</t>
+  </si>
+  <si>
+    <t>Quantity.value</t>
+  </si>
+  <si>
+    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
+  </si>
+  <si>
+    <t>SN.2  / CQ - N/A</t>
+  </si>
+  <si>
+    <t>Medication.amount.numerator.comparator</t>
+  </si>
+  <si>
+    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+  </si>
+  <si>
+    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
+  </si>
+  <si>
+    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
+  </si>
+  <si>
+    <t>If there is no comparator, then there is no modification of the value</t>
+  </si>
+  <si>
+    <t>How the Quantity should be understood and represented.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
+  </si>
+  <si>
+    <t>Quantity.comparator</t>
+  </si>
+  <si>
+    <t>IVL properties</t>
+  </si>
+  <si>
+    <t>SN.1  / CQ.1</t>
+  </si>
+  <si>
+    <t>Medication.amount.numerator.unit</t>
+  </si>
+  <si>
+    <t>Unit representation</t>
+  </si>
+  <si>
+    <t>A human-readable form of the unit.</t>
+  </si>
+  <si>
+    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
+  </si>
+  <si>
+    <t>Quantity.unit</t>
+  </si>
+  <si>
+    <t>PQ.unit</t>
+  </si>
+  <si>
+    <t>(see OBX.6 etc.) / CQ.2</t>
+  </si>
+  <si>
+    <t>Medication.amount.numerator.system</t>
+  </si>
+  <si>
+    <t>System that defines coded unit form</t>
+  </si>
+  <si>
+    <t>The identification of the system that provides the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Need to know the system that defines the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Quantity.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qty-3
+</t>
+  </si>
+  <si>
+    <t>CO.codeSystem, PQ.translation.codeSystem</t>
+  </si>
+  <si>
+    <t>Medication.amount.numerator.code</t>
+  </si>
+  <si>
+    <t>Coded form of the unit</t>
+  </si>
+  <si>
+    <t>A computer processable form of the unit in some unit representation system.</t>
+  </si>
+  <si>
+    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+  </si>
+  <si>
+    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/ValueSet-elga-medikationmengenart</t>
+  </si>
+  <si>
+    <t>Quantity.code</t>
+  </si>
+  <si>
+    <t>PQ.code, MO.currency, PQ.translation.code</t>
+  </si>
+  <si>
+    <t>Medication.amount.denominator</t>
+  </si>
+  <si>
+    <t>Denominator value</t>
+  </si>
+  <si>
+    <t>The value of the denominator.</t>
+  </si>
+  <si>
+    <t>Ratio.denominator</t>
+  </si>
+  <si>
+    <t>.denominator</t>
+  </si>
+  <si>
+    <t>Medication.amount.denominator.id</t>
+  </si>
+  <si>
+    <t>Medication.amount.denominator.extension</t>
+  </si>
+  <si>
+    <t>Medication.amount.denominator.value</t>
+  </si>
+  <si>
+    <t>Medication.amount.denominator.comparator</t>
+  </si>
+  <si>
+    <t>Medication.amount.denominator.unit</t>
+  </si>
+  <si>
+    <t>Medication.amount.denominator.system</t>
+  </si>
+  <si>
+    <t>Medication.amount.denominator.code</t>
   </si>
   <si>
     <t>Medication.ingredient</t>
@@ -632,7 +856,7 @@
 </t>
   </si>
   <si>
-    <t>Active or inactive ingredient</t>
+    <t>Wirkstoffe.</t>
   </si>
   <si>
     <t>Identifies a particular constituent of interest in the product.</t>
@@ -647,29 +871,7 @@
     <t>Medication.ingredient.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Medication.ingredient.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Medication.ingredient.modifierExtension</t>
@@ -693,7 +895,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Substance|4.0.1|Medication|4.0.1)</t>
+Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-wirkstoff|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation)</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>
@@ -705,20 +907,300 @@
     <t>The ingredient may reference a substance (for example, amoxicillin) or another medication (for example in the case of a compounded product, Glaxal Base).</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>.player</t>
   </si>
   <si>
     <t>RXC-2-Component Code  if medication: RXO-1-Requested Give Code / RXE-2-Give Code / RXD-2-Dispense/Give Code / RXG-4-Give Code / RXA-5-Administered Code</t>
   </si>
   <si>
-    <t>Medication.ingredient.isActive</t>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept</t>
+  </si>
+  <si>
+    <t>itemCodeableConcept</t>
+  </si>
+  <si>
+    <t>Inhaltsstoff codiert. Wirkstoff-Codes stammen aus der ATC-Klassifikation (Anatomical Therapeutic Chemical Classification), die von der WHO herausgegeben wird. Weitere Codes, wie auch die deutsche Bezeichnung der Codes, entsprechen dem GKV-Arzneimittelindex im Wissenschaftlichen Institut der AOK (WidO), AOK Bundesverband GbR, Deutschland, welcher auf den WHO ATC basiert. Zusätzlich kommen ergänzende Codes aus dem Arzneimittelverzeichnis der AGES zum Einsatz.</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:ATCWidO</t>
+  </si>
+  <si>
+    <t>ATCWidO</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:ATCWidO.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:ATCWidO.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:ATCWidO.system</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>TODO</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:ATCWidO.version</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:ATCWidO.code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:ATCWidO.display</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:ATCWidO.userSelected</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.userSelected</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
 </t>
   </si>
   <si>
-    <t>Active ingredient indicator</t>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:WirkstoffeAges</t>
+  </si>
+  <si>
+    <t>WirkstoffeAges</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-wirkstoffe-ages</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:WirkstoffeAges.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:WirkstoffeAges.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:WirkstoffeAges.system</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:WirkstoffeAges.version</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:WirkstoffeAges.code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:WirkstoffeAges.display</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:WirkstoffeAges.userSelected</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemReference</t>
+  </si>
+  <si>
+    <t>itemReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-wirkstoff|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation)
+</t>
+  </si>
+  <si>
+    <t>Referenz auf Substance oder enthaltene Medikation von magistraler Anwendung.</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.isActive</t>
+  </si>
+  <si>
+    <t>Aktive Wirkstoff TRUE/FALSE</t>
   </si>
   <si>
     <t>Indication of whether this ingredient affects the therapeutic action of the drug.</t>
@@ -734,7 +1216,7 @@
     <t>Medication.ingredient.strength</t>
   </si>
   <si>
-    <t>Quantity of ingredient present</t>
+    <t>Menge der vorhandenen Zutaten.</t>
   </si>
   <si>
     <t>Specifies how many (or how much) of the items there are in this Medication.  For example, 250 mg per tablet.  This is expressed as a ratio where the numerator is 250mg and the denominator is 1 tablet.</t>
@@ -749,7 +1231,7 @@
     <t>Medication.batch</t>
   </si>
   <si>
-    <t>Details about packaged medications</t>
+    <t>Informationen zur Charge des Arzneimittels.</t>
   </si>
   <si>
     <t>Information that only applies to packages (not products).</t>
@@ -924,6 +1406,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1105,12 +1602,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN29"/>
+  <dimension ref="A1:AN69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="32.79296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="32.79296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="71.125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.75" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="18.3359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1118,7 +1615,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="36.54296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="154.70703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1133,10 +1630,10 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="47.4921875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.22265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="55.5546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1271,7 +1768,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1396,13 +1893,13 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>21</v>
@@ -1516,7 +2013,7 @@
         <v>87</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>21</v>
@@ -1609,7 +2106,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>100</v>
       </c>
@@ -1625,7 +2122,7 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
@@ -1723,7 +2220,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>106</v>
       </c>
@@ -1856,7 +2353,7 @@
         <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>
@@ -1951,7 +2448,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>123</v>
       </c>
@@ -2065,7 +2562,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>131</v>
       </c>
@@ -2179,7 +2676,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>139</v>
       </c>
@@ -2295,7 +2792,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>144</v>
       </c>
@@ -2428,7 +2925,7 @@
         <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>21</v>
@@ -2523,7 +3020,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>163</v>
       </c>
@@ -2539,7 +3036,7 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
@@ -2637,7 +3134,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>171</v>
       </c>
@@ -2768,7 +3265,7 @@
         <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
@@ -2812,13 +3309,11 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="Y15" s="2"/>
+      <c r="Z15" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -2851,24 +3346,24 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AM15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>187</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2882,7 +3377,7 @@
         <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
@@ -2891,13 +3386,13 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2948,7 +3443,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -2966,21 +3461,21 @@
         <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" hidden="true">
+      <c r="A17" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AM16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>193</v>
-      </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2991,7 +3486,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
@@ -3003,17 +3498,15 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M17" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>197</v>
-      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
@@ -3062,50 +3555,50 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" hidden="true">
+      <c r="A18" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AM17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>199</v>
-      </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
@@ -3117,15 +3610,17 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>134</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3162,16 +3657,16 @@
         <v>21</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>21</v>
+        <v>202</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>203</v>
@@ -3180,19 +3675,19 @@
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>21</v>
@@ -3203,43 +3698,41 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>134</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3288,25 +3781,25 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>21</v>
@@ -3315,48 +3808,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>133</v>
+        <v>193</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
       </c>
@@ -3404,25 +3893,25 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>130</v>
+        <v>197</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>21</v>
@@ -3431,23 +3920,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -3459,18 +3948,18 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>214</v>
+        <v>133</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
       </c>
@@ -3506,51 +3995,51 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>21</v>
+        <v>202</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>219</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3570,20 +4059,22 @@
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="O22" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -3632,7 +4123,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3650,21 +4141,21 @@
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>21</v>
+        <v>220</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3681,70 +4172,74 @@
         <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>189</v>
+        <v>107</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="P23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="R23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="AA23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q23" s="2"/>
-      <c r="R23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3759,10 +4254,10 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
@@ -3771,7 +4266,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>231</v>
       </c>
@@ -3796,10 +4291,10 @@
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>232</v>
@@ -3808,7 +4303,9 @@
         <v>233</v>
       </c>
       <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -3856,7 +4353,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3871,24 +4368,24 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>21</v>
+        <v>237</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3908,19 +4405,21 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>200</v>
+        <v>101</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>201</v>
+        <v>239</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>202</v>
+        <v>240</v>
       </c>
       <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+      <c r="O25" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>21</v>
       </c>
@@ -3968,7 +4467,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>203</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -3977,64 +4476,66 @@
         <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>21</v>
+        <v>237</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>134</v>
+        <v>246</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>206</v>
+        <v>247</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4058,13 +4559,11 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4082,75 +4581,71 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>207</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>204</v>
+        <v>252</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>21</v>
+        <v>237</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>210</v>
+        <v>254</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -4198,25 +4693,25 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>212</v>
+        <v>256</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>130</v>
+        <v>257</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
@@ -4225,12 +4720,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4253,13 +4748,13 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>239</v>
+        <v>194</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>240</v>
+        <v>195</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4310,7 +4805,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4322,38 +4817,38 @@
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>149</v>
+        <v>197</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>241</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -4365,15 +4860,17 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>243</v>
+        <v>133</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -4410,46 +4907,4634 @@
         <v>21</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>21</v>
+        <v>202</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
+      <c r="A30" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="P30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="P31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q31" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="R31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
+      <c r="A32" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="P32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="33" hidden="true">
+      <c r="A33" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="P33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AG29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
+      <c r="AG33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK29" t="s" s="2">
+      <c r="AK33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="34" hidden="true">
+      <c r="A34" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="P34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="P38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="P39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AC39" s="2"/>
+      <c r="AD39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="P40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AC43" s="2"/>
+      <c r="AD43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="D52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="Y52" s="2"/>
+      <c r="Z52" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="D61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK64" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AL29" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>247</v>
+      <c r="AL64" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>404</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN69">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI68">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2525" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2524" uniqueCount="405">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -982,6 +982,9 @@
     <t>ATCWidO</t>
   </si>
   <si>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/AtElgaEmedValueSetATC</t>
+  </si>
+  <si>
     <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:ATCWidO.id</t>
   </si>
   <si>
@@ -1010,9 +1013,6 @@
   </si>
   <si>
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>TODO</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -6613,13 +6613,11 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>21</v>
+        <v>307</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -6666,10 +6664,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6778,10 +6776,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6892,10 +6890,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6921,16 +6919,16 @@
         <v>101</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -6940,7 +6938,7 @@
         <v>21</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>317</v>
+        <v>21</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>21</v>
@@ -7585,7 +7583,7 @@
         <v>358</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7697,7 +7695,7 @@
         <v>359</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7811,7 +7809,7 @@
         <v>360</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7837,16 +7835,16 @@
         <v>101</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$81</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2524" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2951" uniqueCount="459">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -297,7 +297,7 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
+    <t>Technische id der Ressource</t>
   </si>
   <si>
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
@@ -329,14 +329,191 @@
 </t>
   </si>
   <si>
-    <t>Medication.implicitRules</t>
+    <t>Medication.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Medication.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Medication.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Medication.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Medication.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Medication.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Medication.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Medication.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Medication.implicitRules</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: Die Ressource wird nach den Regeln dieses Implementierungsleitfadens interpretiert. Zusätzliche implizite Verarbeitungsregeln werden nicht verwendet.</t>
   </si>
   <si>
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
@@ -402,6 +579,59 @@
     <t>Act.text?</t>
   </si>
   <si>
+    <t>Medication.text.id</t>
+  </si>
+  <si>
+    <t>Medication.text.extension</t>
+  </si>
+  <si>
+    <t>Medication.text.status</t>
+  </si>
+  <si>
+    <t>generated | extensions | additional | empty</t>
+  </si>
+  <si>
+    <t>The status of the narrative - whether it's entirely generated (from just the defined data or the extensions too), or whether a human authored it and it may contain additional data.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>The status of a resource narrative.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/narrative-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Narrative.status</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Medication.text.div</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xhtml
+</t>
+  </si>
+  <si>
+    <t>Limited xhtml content</t>
+  </si>
+  <si>
+    <t>The actual narrative content, a stripped down version of XHTML.</t>
+  </si>
+  <si>
+    <t>The contents of the html element are an XHTML fragment containing only the basic html formatting elements described in chapters 7-11 and 15 of the HTML 4.0 standard, &lt;a&gt; elements (either name or href), images and internally contained stylesheets. The XHTML content SHALL NOT contain a head, a body, external stylesheet references, scripts, forms, base/link/xlink, frames, iframes and objects.</t>
+  </si>
+  <si>
+    <t>Narrative.div</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+txt-1:The narrative SHALL contain only the basic html formatting elements and attributes described in chapters 7-11 (except section 4 of chapter 9) and 15 of the HTML 4.0 standard, &lt;a&gt; elements (either name or href), images and internally contained style attributes {htmlChecks()}txt-2:The narrative SHALL have some non-whitespace content {htmlChecks()}</t>
+  </si>
+  <si>
     <t>Medication.contained</t>
   </si>
   <si>
@@ -425,47 +655,22 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Medication.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
     <t>Medication.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Fachliche Begründung: Für den Medikationsplan sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -507,9 +712,6 @@
   </si>
   <si>
     <t>Depending on the context of use, the code that was actually selected by the user (prescriber, dispenser, etc.) will have the coding.userSelected set to true.  As described in the coding datatype: "A coding may be marked as a "userSelected" if a user selected the particular coded value in a user interface (e.g. the user selects an item in a pick-list). If a user selected coding exists, it is the preferred choice for performing translations etc. Other codes can only be literal translations to alternative code systems, or codes at a lower level of granularity (e.g. a generic code for a vendor-specific primary one).</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>A coded concept that defines the type of a medication.</t>
@@ -546,9 +748,6 @@
     <t>This status is intended to identify if the medication in a local system is in active use within a drug database or inventory.  For example, a pharmacy system may create a new drug file record for a compounded product "ABC Hospital Special Cream" with an active status.  At some point in the future, it may be determined that the drug record was created with an error and the status is changed to "entered in error".   This status is not intended to specify if a medication is part of a particular formulary.  It is possible that the drug record may be referenced by multiple formularies or catalogues and each of those entries would have a separate status.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>A coded concept defining if the medication is in active use.</t>
   </si>
   <si>
@@ -628,39 +827,7 @@
     <t>Medication.amount.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Medication.amount.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Medication.amount.numerator</t>
@@ -888,6 +1055,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
@@ -945,10 +1115,6 @@
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
   </si>
   <si>
     <t>Code defined by a terminology system</t>
@@ -1602,7 +1768,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN69"/>
+  <dimension ref="A1:AN81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="71.125" customWidth="true" bestFit="true"/>
@@ -1629,7 +1795,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="47.4921875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="55.5546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -2122,16 +2288,16 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>101</v>
@@ -2142,9 +2308,7 @@
       <c r="M5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>104</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>21</v>
@@ -2193,25 +2357,25 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH5" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI5" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK5" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL5" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="AG5" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH5" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI5" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ5" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK5" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL5" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>21</v>
@@ -2229,14 +2393,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>21</v>
@@ -2248,16 +2412,16 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2283,49 +2447,49 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>21</v>
@@ -2336,14 +2500,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2359,10 +2523,10 @@
         <v>21</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>118</v>
@@ -2439,53 +2603,53 @@
         <v>21</v>
       </c>
       <c r="AL7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="AM7" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" hidden="true">
-      <c r="A8" t="s" s="2">
-        <v>123</v>
-      </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2535,25 +2699,25 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>21</v>
@@ -2564,21 +2728,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -2587,19 +2751,19 @@
         <v>21</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2649,25 +2813,25 @@
         <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>21</v>
@@ -2676,48 +2840,46 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
       </c>
@@ -2765,7 +2927,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2777,13 +2939,13 @@
         <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>21</v>
@@ -2794,10 +2956,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2820,16 +2982,16 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2855,13 +3017,13 @@
         <v>21</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>21</v>
@@ -2879,7 +3041,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2897,21 +3059,21 @@
         <v>21</v>
       </c>
       <c r="AL11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN11" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" hidden="true">
+      <c r="A12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="AM11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>151</v>
-      </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2922,10 +3084,10 @@
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>21</v>
@@ -2934,16 +3096,16 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N12" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2969,37 +3131,37 @@
         <v>21</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="Y12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>151</v>
-      </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>21</v>
@@ -3008,24 +3170,24 @@
         <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>162</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3048,16 +3210,16 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3083,13 +3245,13 @@
         <v>21</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>167</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>168</v>
+        <v>21</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
@@ -3107,7 +3269,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3125,7 +3287,7 @@
         <v>21</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>21</v>
@@ -3136,10 +3298,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3159,18 +3321,20 @@
         <v>21</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -3195,13 +3359,13 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>21</v>
+        <v>167</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3219,7 +3383,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3234,28 +3398,28 @@
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>178</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3274,16 +3438,16 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3309,11 +3473,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3331,7 +3497,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3346,24 +3512,24 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3377,22 +3543,22 @@
         <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>101</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>103</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3443,7 +3609,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>187</v>
+        <v>104</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3455,13 +3621,13 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>191</v>
+        <v>105</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>21</v>
@@ -3472,21 +3638,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
@@ -3498,15 +3664,17 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>194</v>
+        <v>109</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
@@ -3543,37 +3711,37 @@
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>115</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>197</v>
+        <v>105</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>21</v>
@@ -3582,26 +3750,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
@@ -3610,17 +3778,15 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>134</v>
+        <v>182</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3645,49 +3811,49 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>21</v>
@@ -3698,10 +3864,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3721,18 +3887,20 @@
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3781,10 +3949,10 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>87</v>
@@ -3793,13 +3961,13 @@
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>195</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>21</v>
@@ -3810,21 +3978,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>21</v>
+        <v>197</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -3836,15 +4004,17 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3893,13 +4063,13 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
@@ -3911,7 +4081,7 @@
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>21</v>
@@ -3922,14 +4092,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3948,16 +4118,16 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3995,19 +4165,19 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4019,13 +4189,13 @@
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
@@ -4036,10 +4206,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4050,32 +4220,28 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>213</v>
+        <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4123,39 +4289,39 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>220</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4166,36 +4332,34 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>107</v>
+        <v>211</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q23" t="s" s="2">
-        <v>225</v>
-      </c>
+      <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
         <v>21</v>
       </c>
@@ -4215,13 +4379,13 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>167</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -4239,13 +4403,13 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>21</v>
@@ -4257,21 +4421,21 @@
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>21</v>
+        <v>216</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4285,7 +4449,7 @@
         <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
@@ -4294,18 +4458,18 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4329,13 +4493,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>21</v>
+        <v>223</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4353,7 +4517,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4368,24 +4532,24 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4396,30 +4560,30 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
       </c>
@@ -4443,13 +4607,13 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>21</v>
+        <v>232</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
@@ -4467,7 +4631,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4476,7 +4640,7 @@
         <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>99</v>
@@ -4485,21 +4649,21 @@
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4507,13 +4671,13 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>21</v>
@@ -4522,20 +4686,16 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>107</v>
+        <v>236</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4559,11 +4719,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4581,7 +4743,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4596,24 +4758,24 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4627,24 +4789,26 @@
         <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -4669,13 +4833,11 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -4693,7 +4855,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4708,24 +4870,24 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4739,22 +4901,22 @@
         <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>193</v>
+        <v>252</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>195</v>
+        <v>254</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4805,7 +4967,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>196</v>
+        <v>251</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4817,13 +4979,13 @@
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>197</v>
+        <v>255</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>21</v>
@@ -4834,21 +4996,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -4860,17 +5022,15 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -4907,37 +5067,37 @@
         <v>21</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>203</v>
+        <v>104</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>197</v>
+        <v>105</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
@@ -4948,21 +5108,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -4971,23 +5131,21 @@
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>213</v>
+        <v>108</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>214</v>
+        <v>109</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>110</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -4996,7 +5154,7 @@
         <v>21</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>21</v>
@@ -5023,51 +5181,51 @@
         <v>21</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>218</v>
+        <v>115</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>219</v>
+        <v>105</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>220</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5075,39 +5233,35 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>107</v>
+        <v>259</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>222</v>
+        <v>260</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>223</v>
+        <v>261</v>
       </c>
       <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>224</v>
-      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q31" t="s" s="2">
-        <v>225</v>
-      </c>
+      <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5127,13 +5281,13 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>167</v>
+        <v>21</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -5151,7 +5305,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5169,21 +5323,21 @@
         <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>229</v>
+        <v>263</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>230</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5194,7 +5348,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5203,21 +5357,19 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>232</v>
+        <v>102</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>233</v>
+        <v>103</v>
       </c>
       <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>234</v>
-      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5265,7 +5417,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>235</v>
+        <v>104</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5277,38 +5429,38 @@
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>236</v>
+        <v>105</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5317,21 +5469,21 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>239</v>
+        <v>109</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -5367,51 +5519,51 @@
         <v>21</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>242</v>
+        <v>115</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5422,7 +5574,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
@@ -5434,19 +5586,19 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>267</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5495,7 +5647,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5513,21 +5665,21 @@
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>237</v>
+        <v>274</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5535,37 +5687,39 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I35" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I35" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J35" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>266</v>
+        <v>163</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q35" s="2"/>
+      <c r="Q35" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="R35" t="s" s="2">
         <v>21</v>
       </c>
@@ -5585,13 +5739,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>21</v>
+        <v>280</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>21</v>
+        <v>281</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -5609,13 +5763,13 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
@@ -5627,21 +5781,21 @@
         <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>21</v>
+        <v>284</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5661,19 +5815,21 @@
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>194</v>
+        <v>286</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>195</v>
+        <v>287</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
@@ -5721,7 +5877,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>196</v>
+        <v>289</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5733,38 +5889,38 @@
         <v>21</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>197</v>
+        <v>290</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>21</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>21</v>
@@ -5773,21 +5929,21 @@
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>134</v>
+        <v>293</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -5835,74 +5991,74 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>203</v>
+        <v>296</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>197</v>
+        <v>298</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>21</v>
+        <v>291</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>274</v>
+        <v>21</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>136</v>
+        <v>302</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>142</v>
+        <v>303</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -5927,13 +6083,11 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>21</v>
+        <v>304</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -5951,39 +6105,39 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>130</v>
+        <v>306</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>21</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>278</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>278</v>
+        <v>307</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5991,7 +6145,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>87</v>
@@ -6003,21 +6157,19 @@
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>281</v>
+        <v>309</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>282</v>
-      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6053,20 +6205,22 @@
         <v>21</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AC39" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>284</v>
+        <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>87</v>
@@ -6078,28 +6232,26 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>285</v>
+        <v>311</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>286</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>21</v>
       </c>
@@ -6120,18 +6272,16 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>289</v>
+        <v>102</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>281</v>
+        <v>103</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>282</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
@@ -6179,10 +6329,10 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>278</v>
+        <v>104</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>87</v>
@@ -6191,38 +6341,38 @@
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>285</v>
+        <v>105</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>286</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6234,15 +6384,17 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>194</v>
+        <v>109</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6279,37 +6431,37 @@
         <v>21</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>196</v>
+        <v>115</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>197</v>
+        <v>105</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
@@ -6320,21 +6472,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -6343,21 +6495,23 @@
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>133</v>
+        <v>267</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>134</v>
+        <v>268</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>199</v>
+        <v>269</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6366,7 +6520,7 @@
         <v>21</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>21</v>
@@ -6393,51 +6547,51 @@
         <v>21</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>203</v>
+        <v>272</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>197</v>
+        <v>273</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6448,36 +6602,36 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>296</v>
+        <v>163</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q43" s="2"/>
+      <c r="Q43" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="R43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6497,35 +6651,37 @@
         <v>21</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>21</v>
+        <v>280</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>21</v>
+        <v>281</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AC43" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
@@ -6537,25 +6693,23 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>304</v>
+        <v>284</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6564,10 +6718,10 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -6576,19 +6730,17 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>296</v>
+        <v>101</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -6613,11 +6765,13 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>307</v>
+        <v>21</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -6635,13 +6789,13 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
@@ -6653,21 +6807,21 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>304</v>
+        <v>291</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6687,19 +6841,21 @@
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>193</v>
+        <v>129</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>194</v>
+        <v>293</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>195</v>
+        <v>294</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -6747,7 +6903,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>196</v>
+        <v>296</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6756,41 +6912,41 @@
         <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>197</v>
+        <v>298</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>21</v>
+        <v>291</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -6799,21 +6955,23 @@
         <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>134</v>
+        <v>300</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>199</v>
+        <v>301</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -6849,51 +7007,51 @@
         <v>21</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>203</v>
+        <v>305</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>197</v>
+        <v>306</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>21</v>
+        <v>291</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6904,32 +7062,30 @@
         <v>87</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>101</v>
+        <v>320</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -6977,13 +7133,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -6995,21 +7151,21 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>320</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7029,20 +7185,18 @@
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>323</v>
+        <v>102</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7091,7 +7245,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>326</v>
+        <v>104</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7103,38 +7257,38 @@
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>327</v>
+        <v>105</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>328</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
@@ -7143,21 +7297,21 @@
         <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>331</v>
+        <v>109</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7205,72 +7359,74 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>334</v>
+        <v>115</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>335</v>
+        <v>105</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>336</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
@@ -7319,39 +7475,39 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>343</v>
+        <v>188</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>344</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7359,7 +7515,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>87</v>
@@ -7371,22 +7527,20 @@
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -7423,22 +7577,20 @@
         <v>21</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>21</v>
+        <v>339</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>87</v>
@@ -7450,27 +7602,27 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>354</v>
+        <v>341</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>295</v>
+        <v>333</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>21</v>
@@ -7483,28 +7635,26 @@
         <v>87</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>296</v>
+        <v>218</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>297</v>
+        <v>344</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>300</v>
+        <v>337</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -7529,11 +7679,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>357</v>
+        <v>21</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -7551,13 +7703,13 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
@@ -7566,24 +7718,24 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>303</v>
+        <v>340</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>304</v>
+        <v>341</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7606,13 +7758,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>194</v>
+        <v>102</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>195</v>
+        <v>103</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7663,7 +7815,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>196</v>
+        <v>104</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7681,7 +7833,7 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>197</v>
+        <v>105</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>21</v>
@@ -7692,14 +7844,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7718,16 +7870,16 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>199</v>
+        <v>110</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7765,19 +7917,19 @@
         <v>21</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>200</v>
+        <v>112</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>201</v>
+        <v>113</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>202</v>
+        <v>114</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>203</v>
+        <v>115</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7789,13 +7941,13 @@
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>197</v>
+        <v>105</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
@@ -7806,10 +7958,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>313</v>
+        <v>350</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7817,10 +7969,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
@@ -7832,19 +7984,19 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>314</v>
+        <v>351</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>315</v>
+        <v>352</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>316</v>
+        <v>353</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>317</v>
+        <v>354</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -7881,25 +8033,23 @@
         <v>21</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
@@ -7911,23 +8061,25 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="C56" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="D56" t="s" s="2">
         <v>21</v>
       </c>
@@ -7939,7 +8091,7 @@
         <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>21</v>
@@ -7948,18 +8100,20 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>193</v>
+        <v>141</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>324</v>
+        <v>352</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -7983,13 +8137,11 @@
         <v>21</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>21</v>
@@ -8007,13 +8159,13 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
@@ -8025,13 +8177,13 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>328</v>
+        <v>358</v>
       </c>
     </row>
     <row r="57" hidden="true">
@@ -8039,7 +8191,7 @@
         <v>362</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>330</v>
+        <v>363</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8059,21 +8211,19 @@
         <v>21</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>331</v>
+        <v>102</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>332</v>
+        <v>103</v>
       </c>
       <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>333</v>
-      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8121,7 +8271,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>334</v>
+        <v>104</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8133,38 +8283,38 @@
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>335</v>
+        <v>105</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>336</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>338</v>
+        <v>365</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
@@ -8173,21 +8323,21 @@
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>339</v>
+        <v>109</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8223,51 +8373,51 @@
         <v>21</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>342</v>
+        <v>115</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>343</v>
+        <v>105</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>344</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8275,7 +8425,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>87</v>
@@ -8290,19 +8440,19 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>347</v>
+        <v>129</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8351,7 +8501,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8369,21 +8519,21 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>354</v>
+        <v>374</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8406,20 +8556,18 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -8467,7 +8615,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8485,25 +8633,23 @@
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>21</v>
       </c>
@@ -8515,26 +8661,26 @@
         <v>87</v>
       </c>
       <c r="H61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K61" t="s" s="2">
-        <v>376</v>
+        <v>163</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>281</v>
+        <v>386</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>282</v>
+        <v>387</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -8583,10 +8729,10 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>278</v>
+        <v>388</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>87</v>
@@ -8598,24 +8744,24 @@
         <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>285</v>
+        <v>389</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>286</v>
+        <v>390</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8629,26 +8775,26 @@
         <v>87</v>
       </c>
       <c r="H62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J62" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K62" t="s" s="2">
-        <v>347</v>
+        <v>101</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -8697,7 +8843,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8715,21 +8861,21 @@
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>21</v>
+        <v>398</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8743,25 +8889,29 @@
         <v>87</v>
       </c>
       <c r="H63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K63" t="s" s="2">
-        <v>188</v>
+        <v>401</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -8809,7 +8959,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>383</v>
+        <v>406</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8824,26 +8974,28 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>386</v>
+        <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>191</v>
+        <v>407</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>387</v>
+        <v>408</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="D64" t="s" s="2">
         <v>21</v>
       </c>
@@ -8852,28 +9004,32 @@
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>266</v>
+        <v>141</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>389</v>
+        <v>351</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
@@ -8897,13 +9053,11 @@
         <v>21</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>21</v>
+        <v>411</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -8921,13 +9075,13 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>388</v>
+        <v>356</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
@@ -8936,24 +9090,24 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>391</v>
+        <v>357</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>21</v>
+        <v>358</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>392</v>
+        <v>363</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8976,13 +9130,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>194</v>
+        <v>102</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>195</v>
+        <v>103</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9033,7 +9187,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>196</v>
+        <v>104</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9051,7 +9205,7 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>197</v>
+        <v>105</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>21</v>
@@ -9062,14 +9216,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>393</v>
+        <v>365</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9088,16 +9242,16 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>199</v>
+        <v>110</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9135,19 +9289,19 @@
         <v>21</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>203</v>
+        <v>115</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9159,13 +9313,13 @@
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>197</v>
+        <v>105</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>21</v>
@@ -9176,45 +9330,45 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>394</v>
+        <v>367</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>274</v>
+        <v>21</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>275</v>
+        <v>368</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>276</v>
+        <v>369</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>136</v>
+        <v>370</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>142</v>
+        <v>371</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -9263,39 +9417,39 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>277</v>
+        <v>372</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>130</v>
+        <v>373</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>21</v>
+        <v>374</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9315,18 +9469,20 @@
         <v>21</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -9375,7 +9531,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9390,24 +9546,24 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>149</v>
+        <v>381</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>398</v>
+        <v>382</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9427,19 +9583,21 @@
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>400</v>
+        <v>163</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>401</v>
+        <v>385</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -9487,7 +9645,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9502,20 +9660,1386 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AM69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN69" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>404</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="D73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>458</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN69">
+  <autoFilter ref="A1:AN81">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9525,7 +11049,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI68">
+  <conditionalFormatting sqref="A2:AI80">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1065,7 +1065,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-wirkstoff|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation)</t>
+Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation)</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>
@@ -1356,7 +1356,7 @@
     <t>itemReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-wirkstoff|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation)
 </t>
   </si>
   <si>
@@ -1781,7 +1781,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="154.70703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="87.328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$106</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2951" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3842" uniqueCount="505">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -658,19 +658,91 @@
     <t>Medication.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
+    <t>Medication.extension:Rezeptur</t>
+  </si>
+  <si>
+    <t>Rezeptur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-extension-rezeptur}
+</t>
+  </si>
+  <si>
+    <t>AT ELGA e-Medikation Extension Rezeptur</t>
+  </si>
+  <si>
+    <t>AT ELGA e-Medikation Extension für die Rezeptur für die Zubereitung einer magistralen Zubereitung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Medication.extension:Rezeptur.id</t>
+  </si>
+  <si>
+    <t>Medication.extension.id</t>
+  </si>
+  <si>
+    <t>Medication.extension:Rezeptur.extension</t>
+  </si>
+  <si>
+    <t>Medication.extension.extension</t>
+  </si>
+  <si>
+    <t>Medication.extension:Rezeptur.url</t>
+  </si>
+  <si>
+    <t>Medication.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-extension-rezeptur</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Medication.extension:Rezeptur.value[x]</t>
+  </si>
+  <si>
+    <t>Medication.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">markdown
+</t>
+  </si>
+  <si>
+    <t>Angabe der Rezeptur für die Zubereitung</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
     <t>Medication.modifierExtension</t>
   </si>
   <si>
     <t>Fachliche Begründung: Für den Medikationsplan sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
-  </si>
-  <si>
-    <t>An Extension</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -705,7 +777,7 @@
 </t>
   </si>
   <si>
-    <t>Code des Arzneimittels.</t>
+    <t>Codes that identify this medication</t>
   </si>
   <si>
     <t>A code (or set of codes) that specify this medication, or a textual description if no code is available. Usage note: This could be a standard medication code such as a code from RxNorm, SNOMED CT, IDMP etc. It could also be a national or local formulary code, optionally with translations to other code systems.</t>
@@ -736,6 +808,60 @@
     <t>RXO-1.1-Requested Give Code.code / RXE-2.1-Give Code.code / RXD-2.1-Dispense/Give Code.code / RXG-4.1-Give Code.code /RXA-5.1-Administered Code.code / RXC-2.1 Component Code</t>
   </si>
   <si>
+    <t>Medication.code.id</t>
+  </si>
+  <si>
+    <t>Medication.code.extension</t>
+  </si>
+  <si>
+    <t>Medication.code.coding</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Medication.code.text</t>
+  </si>
+  <si>
+    <t>Titel der Medikation</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
     <t>Medication.status</t>
   </si>
   <si>
@@ -886,7 +1012,7 @@
     <t>Medication.amount.numerator.comparator</t>
   </si>
   <si>
-    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+    <t>Fachliche Begründung: TODO</t>
   </si>
   <si>
     <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
@@ -1007,6 +1133,9 @@
     <t>Medication.amount.denominator.comparator</t>
   </si>
   <si>
+    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+  </si>
+  <si>
     <t>Medication.amount.denominator.unit</t>
   </si>
   <si>
@@ -1032,6 +1161,10 @@
     <t>The ingredients need not be a complete list.  If an ingredient is not specified, this does not indicate whether an ingredient is present or absent.  If an ingredient is specified it does not mean that all ingredients are specified.  It is possible to specify both inactive and active ingredients.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:isActive}
+</t>
+  </si>
+  <si>
     <t>.scopesRole[typeCode=INGR]</t>
   </si>
   <si>
@@ -1065,7 +1198,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation)</t>
+Reference(Substance|4.0.1|Medication|4.0.1)</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>
@@ -1077,72 +1210,97 @@
     <t>The ingredient may reference a substance (for example, amoxicillin) or another medication (for example in the case of a compounded product, Glaxal Base).</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
+    <t>.player</t>
+  </si>
+  <si>
+    <t>RXC-2-Component Code  if medication: RXO-1-Requested Give Code / RXE-2-Give Code / RXD-2-Dispense/Give Code / RXG-4-Give Code / RXA-5-Administered Code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.isActive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
 </t>
   </si>
   <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>.player</t>
-  </si>
-  <si>
-    <t>RXC-2-Component Code  if medication: RXO-1-Requested Give Code / RXE-2-Give Code / RXD-2-Dispense/Give Code / RXG-4-Give Code / RXA-5-Administered Code</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept</t>
-  </si>
-  <si>
-    <t>itemCodeableConcept</t>
+    <t>Active ingredient indicator</t>
+  </si>
+  <si>
+    <t>Indication of whether this ingredient affects the therapeutic action of the drug.</t>
+  </si>
+  <si>
+    <t>True indicates that the ingredient affects the therapeutic action of the drug (i.e. active). +False indicates that the ingredient does not affect the therapeutic action of the drug (i.e. inactive).</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.strength</t>
+  </si>
+  <si>
+    <t>Quantity of ingredient present</t>
+  </si>
+  <si>
+    <t>Specifies how many (or how much) of the items there are in this Medication.  For example, 250 mg per tablet.  This is expressed as a ratio where the numerator is 250mg and the denominator is 1 tablet.</t>
+  </si>
+  <si>
+    <t>//element(*,DrugCodedType)/Strength</t>
+  </si>
+  <si>
+    <t>RXC-3-Component Amount &amp; RXC-4-Component Units  if medication: RXO-2-Requested Give Amount - Minimum &amp; RXO-4-Requested Give Units / RXO-3-Requested Give Amount - Maximum &amp; RXO-4-Requested Give Units / RXO-11-Requested Dispense Amount &amp; RXO-12-Requested Dispense Units / RXE-3-Give Amount - Minimum &amp; RXE-5-Give Units / RXE-4-Give Amount - Maximum &amp; RXE-5-Give Units / RXE-10-Dispense Amount &amp; RXE-10-Dispense Units</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient</t>
+  </si>
+  <si>
+    <t>activeIngredient</t>
+  </si>
+  <si>
+    <t>Active or inactive ingredient</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.modifierExtension</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: Es sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x]</t>
   </si>
   <si>
     <t>Inhaltsstoff codiert. Wirkstoff-Codes stammen aus der ATC-Klassifikation (Anatomical Therapeutic Chemical Classification), die von der WHO herausgegeben wird. Weitere Codes, wie auch die deutsche Bezeichnung der Codes, entsprechen dem GKV-Arzneimittelindex im Wissenschaftlichen Institut der AOK (WidO), AOK Bundesverband GbR, Deutschland, welcher auf den WHO ATC basiert. Zusätzlich kommen ergänzende Codes aus dem Arzneimittelverzeichnis der AGES zum Einsatz.</t>
   </si>
   <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.id</t>
+    <t>Medication.ingredient:activeIngredient.item[x].id</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].id</t>
   </si>
   <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.extension</t>
+    <t>Medication.ingredient:activeIngredient.item[x].extension</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].extension</t>
   </si>
   <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding</t>
+    <t>Medication.ingredient:activeIngredient.item[x].coding</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:ATCWidO</t>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO</t>
   </si>
   <si>
     <t>ATCWidO</t>
@@ -1151,19 +1309,19 @@
     <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/AtElgaEmedValueSetATC</t>
   </si>
   <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:ATCWidO.id</t>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.id</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding.id</t>
   </si>
   <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:ATCWidO.extension</t>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.extension</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding.extension</t>
   </si>
   <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:ATCWidO.system</t>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.system</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding.system</t>
@@ -1190,7 +1348,7 @@
     <t>C*E.3</t>
   </si>
   <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:ATCWidO.version</t>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.version</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding.version</t>
@@ -1214,7 +1372,7 @@
     <t>C*E.7</t>
   </si>
   <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:ATCWidO.code</t>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.code</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding.code</t>
@@ -1238,7 +1396,7 @@
     <t>C*E.1</t>
   </si>
   <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:ATCWidO.display</t>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.display</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding.display</t>
@@ -1262,16 +1420,12 @@
     <t>C*E.2 - but note this is not well followed</t>
   </si>
   <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:ATCWidO.userSelected</t>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.userSelected</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding.userSelected</t>
   </si>
   <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
     <t>If this coding was chosen directly by the user</t>
   </si>
   <si>
@@ -1293,7 +1447,7 @@
     <t>Sometimes implied by being first</t>
   </si>
   <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:WirkstoffeAges</t>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges</t>
   </si>
   <si>
     <t>WirkstoffeAges</t>
@@ -1302,96 +1456,82 @@
     <t>https://termgit.elga.gv.at/ValueSet/elga-wirkstoffe-ages</t>
   </si>
   <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:WirkstoffeAges.id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:WirkstoffeAges.extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:WirkstoffeAges.system</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:WirkstoffeAges.version</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:WirkstoffeAges.code</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:WirkstoffeAges.display</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding:WirkstoffeAges.userSelected</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.text</t>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.system</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.version</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.display</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.userSelected</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].text</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].text</t>
   </si>
   <si>
+    <t>Medication.ingredient:activeIngredient.isActive</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.strength</t>
+  </si>
+  <si>
+    <t>Menge der vorhandenen Zutaten.</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient</t>
+  </si>
+  <si>
+    <t>inactiveIngredient</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.modifierExtension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.item[x]</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.item[x].id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.item[x].extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.item[x].coding</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.item[x].text</t>
+  </si>
+  <si>
     <t>Plain text representation of the concept</t>
   </si>
   <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemReference</t>
-  </si>
-  <si>
-    <t>itemReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation)
-</t>
-  </si>
-  <si>
-    <t>Referenz auf Substance oder enthaltene Medikation von magistraler Anwendung.</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.isActive</t>
-  </si>
-  <si>
-    <t>Aktive Wirkstoff TRUE/FALSE</t>
-  </si>
-  <si>
-    <t>Indication of whether this ingredient affects the therapeutic action of the drug.</t>
-  </si>
-  <si>
-    <t>True indicates that the ingredient affects the therapeutic action of the drug (i.e. active). -False indicates that the ingredient does not affect the therapeutic action of the drug (i.e. inactive).</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.strength</t>
-  </si>
-  <si>
-    <t>Menge der vorhandenen Zutaten.</t>
-  </si>
-  <si>
-    <t>Specifies how many (or how much) of the items there are in this Medication.  For example, 250 mg per tablet.  This is expressed as a ratio where the numerator is 250mg and the denominator is 1 tablet.</t>
-  </si>
-  <si>
-    <t>//element(*,DrugCodedType)/Strength</t>
-  </si>
-  <si>
-    <t>RXC-3-Component Amount &amp; RXC-4-Component Units  if medication: RXO-2-Requested Give Amount - Minimum &amp; RXO-4-Requested Give Units / RXO-3-Requested Give Amount - Maximum &amp; RXO-4-Requested Give Units / RXO-11-Requested Dispense Amount &amp; RXO-12-Requested Dispense Units / RXE-3-Give Amount - Minimum &amp; RXE-5-Give Units / RXE-4-Give Amount - Maximum &amp; RXE-5-Give Units / RXE-10-Dispense Amount &amp; RXE-10-Dispense Units</t>
+    <t>Medication.ingredient:inactiveIngredient.isActive</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.strength</t>
   </si>
   <si>
     <t>Medication.batch</t>
@@ -1768,12 +1908,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN81"/>
+  <dimension ref="A1:AN106"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="71.125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="66.546875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.75" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="18.3359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="15.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1781,7 +1921,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="87.328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="77.4921875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2498,7 +2638,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>117</v>
       </c>
@@ -2517,7 +2657,7 @@
         <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>
@@ -2612,7 +2752,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>122</v>
       </c>
@@ -2631,7 +2771,7 @@
         <v>87</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>21</v>
@@ -4099,7 +4239,7 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4121,14 +4261,12 @@
         <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>109</v>
+        <v>204</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -4165,19 +4303,17 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4195,7 +4331,7 @@
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
@@ -4204,14 +4340,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4220,25 +4358,25 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>108</v>
+        <v>209</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4289,7 +4427,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4298,7 +4436,7 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>116</v>
@@ -4318,10 +4456,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4332,7 +4470,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
@@ -4341,20 +4479,18 @@
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>211</v>
+        <v>101</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>212</v>
+        <v>102</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4403,39 +4539,39 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>210</v>
+        <v>104</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" hidden="true">
+      <c r="A24" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="B24" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4446,29 +4582,27 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>218</v>
+        <v>108</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4493,63 +4627,63 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>223</v>
+        <v>21</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>217</v>
+        <v>115</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>225</v>
+        <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4557,31 +4691,31 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4589,7 +4723,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>21</v>
@@ -4607,13 +4741,13 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>232</v>
+        <v>21</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>233</v>
+        <v>21</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
@@ -4631,10 +4765,10 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>87</v>
@@ -4643,13 +4777,13 @@
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>234</v>
+        <v>188</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
@@ -4658,12 +4792,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4671,28 +4805,28 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4743,7 +4877,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4758,24 +4892,24 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>239</v>
+        <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>240</v>
+        <v>188</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4786,29 +4920,27 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I27" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I27" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>218</v>
+        <v>108</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -4833,11 +4965,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>247</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -4855,39 +4989,39 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4898,10 +5032,10 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
@@ -4910,15 +5044,17 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4967,13 +5103,13 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
@@ -4985,21 +5121,21 @@
         <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5013,24 +5149,26 @@
         <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>101</v>
+        <v>241</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>102</v>
+        <v>242</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -5055,13 +5193,13 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>21</v>
+        <v>246</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -5079,7 +5217,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>104</v>
+        <v>240</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5091,38 +5229,38 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>105</v>
+        <v>248</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>21</v>
+        <v>249</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -5134,17 +5272,15 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -5181,31 +5317,31 @@
         <v>21</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>21</v>
@@ -5220,43 +5356,45 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>259</v>
+        <v>108</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>260</v>
+        <v>109</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5293,37 +5431,37 @@
         <v>21</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>262</v>
+        <v>115</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>263</v>
+        <v>105</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
@@ -5334,10 +5472,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5348,7 +5486,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5357,19 +5495,23 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>102</v>
+        <v>254</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5417,73 +5559,75 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>104</v>
+        <v>258</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>109</v>
+        <v>262</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>110</v>
+        <v>263</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -5519,51 +5663,51 @@
         <v>21</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>115</v>
+        <v>266</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>105</v>
+        <v>267</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>21</v>
+        <v>268</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5574,32 +5718,30 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>267</v>
+        <v>163</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
       </c>
@@ -5623,13 +5765,13 @@
         <v>21</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -5647,7 +5789,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5665,21 +5807,21 @@
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>274</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5696,74 +5838,70 @@
         <v>21</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>163</v>
+        <v>277</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="P35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q35" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="R35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5778,24 +5916,24 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>21</v>
+        <v>280</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AM35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN35" t="s" s="2">
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
         <v>284</v>
       </c>
-    </row>
-    <row r="36" hidden="true">
-      <c r="A36" t="s" s="2">
-        <v>285</v>
-      </c>
       <c r="B36" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5809,27 +5947,27 @@
         <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>101</v>
+        <v>241</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>288</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
@@ -5853,13 +5991,11 @@
         <v>21</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -5877,7 +6013,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5892,7 +6028,7 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>290</v>
@@ -5904,7 +6040,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>292</v>
       </c>
@@ -5923,7 +6059,7 @@
         <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -5932,18 +6068,16 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>129</v>
+        <v>293</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>295</v>
-      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -5991,7 +6125,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6000,7 +6134,7 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>297</v>
+        <v>21</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>99</v>
@@ -6009,21 +6143,21 @@
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>291</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6031,35 +6165,31 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>163</v>
+        <v>101</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>300</v>
+        <v>102</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6083,11 +6213,13 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>304</v>
+        <v>21</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -6105,7 +6237,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>305</v>
+        <v>104</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6117,38 +6249,38 @@
         <v>21</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>306</v>
+        <v>105</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>291</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
@@ -6157,18 +6289,20 @@
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>259</v>
+        <v>108</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>308</v>
+        <v>109</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6205,37 +6339,37 @@
         <v>21</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>310</v>
+        <v>115</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>311</v>
+        <v>105</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
@@ -6244,12 +6378,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6257,28 +6391,28 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>101</v>
+        <v>300</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>102</v>
+        <v>301</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>103</v>
+        <v>302</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6329,7 +6463,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>104</v>
+        <v>303</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6341,13 +6475,13 @@
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>105</v>
+        <v>304</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
@@ -6358,21 +6492,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6384,17 +6518,15 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6431,31 +6563,31 @@
         <v>21</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
@@ -6472,21 +6604,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -6495,23 +6627,21 @@
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>267</v>
+        <v>108</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>268</v>
+        <v>109</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>269</v>
+        <v>110</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6520,7 +6650,7 @@
         <v>21</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>21</v>
@@ -6547,51 +6677,51 @@
         <v>21</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>272</v>
+        <v>115</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>273</v>
+        <v>105</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>274</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6608,30 +6738,30 @@
         <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>163</v>
+        <v>308</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>278</v>
+        <v>312</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q43" t="s" s="2">
-        <v>279</v>
-      </c>
+      <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6651,13 +6781,13 @@
         <v>21</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>280</v>
+        <v>21</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>281</v>
+        <v>21</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>21</v>
@@ -6675,7 +6805,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6693,13 +6823,13 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>284</v>
+        <v>315</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -6724,28 +6854,30 @@
         <v>21</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>288</v>
+        <v>319</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q44" s="2"/>
+      <c r="Q44" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="R44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6765,13 +6897,13 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>21</v>
+        <v>321</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>21</v>
+        <v>322</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -6789,7 +6921,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>289</v>
+        <v>323</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6807,21 +6939,21 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>290</v>
+        <v>324</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>291</v>
+        <v>325</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6844,17 +6976,17 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>293</v>
+        <v>327</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>294</v>
+        <v>328</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6903,7 +7035,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>296</v>
+        <v>330</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6912,7 +7044,7 @@
         <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>297</v>
+        <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>99</v>
@@ -6921,21 +7053,21 @@
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>298</v>
+        <v>331</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>291</v>
+        <v>332</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6946,7 +7078,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -6958,19 +7090,17 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>303</v>
+        <v>336</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7019,7 +7149,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>305</v>
+        <v>337</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7028,7 +7158,7 @@
         <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>21</v>
+        <v>338</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>99</v>
@@ -7037,21 +7167,21 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>306</v>
+        <v>339</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>291</v>
+        <v>332</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7062,7 +7192,7 @@
         <v>87</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>88</v>
@@ -7071,21 +7201,23 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>320</v>
+        <v>163</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7109,13 +7241,11 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7133,13 +7263,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -7151,21 +7281,21 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>21</v>
+        <v>332</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7185,16 +7315,16 @@
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>101</v>
+        <v>300</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>102</v>
+        <v>349</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>103</v>
+        <v>350</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7245,7 +7375,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>104</v>
+        <v>351</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7257,13 +7387,13 @@
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>105</v>
+        <v>352</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
@@ -7274,21 +7404,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
@@ -7300,17 +7430,15 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -7359,19 +7487,19 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>21</v>
@@ -7388,14 +7516,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>328</v>
+        <v>107</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7408,26 +7536,24 @@
         <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>329</v>
+        <v>109</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>330</v>
+        <v>110</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O50" t="s" s="2">
-        <v>331</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7463,19 +7589,19 @@
         <v>21</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>332</v>
+        <v>115</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7493,7 +7619,7 @@
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>188</v>
+        <v>105</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
@@ -7504,10 +7630,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7515,7 +7641,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>87</v>
@@ -7527,20 +7653,22 @@
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>334</v>
+        <v>308</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>335</v>
+        <v>309</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="O51" t="s" s="2">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -7550,7 +7678,7 @@
         <v>21</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>21</v>
@@ -7577,20 +7705,22 @@
         <v>21</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AC51" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>339</v>
+        <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>87</v>
@@ -7602,28 +7732,26 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>340</v>
+        <v>314</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>341</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>21</v>
       </c>
@@ -7638,28 +7766,30 @@
         <v>21</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>218</v>
+        <v>163</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q52" s="2"/>
+      <c r="Q52" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="R52" t="s" s="2">
         <v>21</v>
       </c>
@@ -7679,13 +7809,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>21</v>
+        <v>321</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>21</v>
+        <v>322</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -7703,10 +7833,10 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>87</v>
@@ -7718,24 +7848,24 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>341</v>
+        <v>325</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7746,7 +7876,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -7755,19 +7885,21 @@
         <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>102</v>
+        <v>327</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>103</v>
+        <v>328</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -7815,7 +7947,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>104</v>
+        <v>330</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7827,38 +7959,38 @@
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>105</v>
+        <v>331</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>21</v>
+        <v>332</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -7867,21 +7999,21 @@
         <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>109</v>
+        <v>334</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -7917,51 +8049,51 @@
         <v>21</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>115</v>
+        <v>337</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>21</v>
+        <v>338</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>105</v>
+        <v>339</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>21</v>
+        <v>332</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7972,7 +8104,7 @@
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
@@ -7984,19 +8116,19 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8033,23 +8165,25 @@
         <v>21</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AC55" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
@@ -8061,34 +8195,32 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>358</v>
+        <v>332</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>88</v>
@@ -8097,23 +8229,21 @@
         <v>21</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>141</v>
+        <v>362</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8137,29 +8267,29 @@
         <v>21</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y56" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AC56" s="2"/>
+      <c r="AD56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8177,21 +8307,21 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>358</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8300,10 +8430,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8373,16 +8503,16 @@
         <v>21</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>115</v>
@@ -8414,45 +8544,45 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>21</v>
+        <v>371</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>370</v>
+        <v>111</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8501,36 +8631,36 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>373</v>
+        <v>188</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>374</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>376</v>
@@ -8541,7 +8671,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>87</v>
@@ -8553,21 +8683,21 @@
         <v>21</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>101</v>
+        <v>377</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N60" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="O60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -8615,10 +8745,10 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>87</v>
@@ -8630,7 +8760,7 @@
         <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>381</v>
@@ -8647,7 +8777,7 @@
         <v>383</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8667,10 +8797,10 @@
         <v>21</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>163</v>
+        <v>384</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>385</v>
@@ -8729,7 +8859,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8747,21 +8877,21 @@
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>390</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8781,21 +8911,19 @@
         <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>101</v>
+        <v>293</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>395</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -8843,7 +8971,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8858,26 +8986,28 @@
         <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>397</v>
+        <v>296</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="C63" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="D63" t="s" s="2">
         <v>21</v>
       </c>
@@ -8886,32 +9016,30 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>401</v>
+        <v>362</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>403</v>
+        <v>364</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -8959,13 +9087,13 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>406</v>
+        <v>361</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
@@ -8977,25 +9105,23 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>407</v>
+        <v>367</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>408</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>21</v>
       </c>
@@ -9007,29 +9133,25 @@
         <v>87</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>351</v>
+        <v>102</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
@@ -9053,11 +9175,13 @@
         <v>21</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>411</v>
+        <v>21</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -9075,50 +9199,50 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>356</v>
+        <v>104</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>357</v>
+        <v>105</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>358</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -9130,15 +9254,17 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
@@ -9187,19 +9313,19 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>21</v>
@@ -9216,43 +9342,41 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>109</v>
+        <v>400</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -9289,19 +9413,19 @@
         <v>21</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9319,7 +9443,7 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>21</v>
@@ -9328,12 +9452,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9347,28 +9471,26 @@
         <v>87</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>129</v>
+        <v>241</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -9417,10 +9539,10 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>87</v>
@@ -9432,24 +9554,24 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9469,20 +9591,18 @@
         <v>21</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>377</v>
+        <v>102</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -9531,7 +9651,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>380</v>
+        <v>104</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9543,38 +9663,38 @@
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>381</v>
+        <v>105</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>382</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
@@ -9583,21 +9703,21 @@
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>385</v>
+        <v>109</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -9633,51 +9753,51 @@
         <v>21</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>388</v>
+        <v>115</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>389</v>
+        <v>105</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>390</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9685,13 +9805,13 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>21</v>
@@ -9700,17 +9820,19 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>393</v>
+        <v>254</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="O70" t="s" s="2">
-        <v>395</v>
+        <v>257</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -9747,25 +9869,23 @@
         <v>21</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="AC70" s="2"/>
       <c r="AD70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>396</v>
+        <v>258</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
@@ -9777,23 +9897,25 @@
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>397</v>
+        <v>259</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>398</v>
+        <v>260</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="C71" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="D71" t="s" s="2">
         <v>21</v>
       </c>
@@ -9805,7 +9927,7 @@
         <v>87</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>21</v>
@@ -9814,19 +9936,19 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>401</v>
+        <v>141</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>402</v>
+        <v>254</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>403</v>
+        <v>255</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>404</v>
+        <v>256</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>405</v>
+        <v>257</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -9851,13 +9973,11 @@
         <v>21</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>21</v>
+        <v>412</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
@@ -9875,13 +9995,13 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>406</v>
+        <v>258</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
@@ -9893,21 +10013,21 @@
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>407</v>
+        <v>259</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>408</v>
+        <v>260</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9927,23 +10047,19 @@
         <v>21</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>421</v>
+        <v>102</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
       </c>
@@ -9991,7 +10107,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>425</v>
+        <v>104</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10003,43 +10119,41 @@
         <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>426</v>
+        <v>105</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>427</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="C73" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>21</v>
@@ -10048,18 +10162,18 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>430</v>
+        <v>108</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>431</v>
+        <v>109</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>21</v>
       </c>
@@ -10095,51 +10209,51 @@
         <v>21</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>333</v>
+        <v>115</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>340</v>
+        <v>105</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>341</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10147,7 +10261,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>87</v>
@@ -10159,20 +10273,22 @@
         <v>21</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>401</v>
+        <v>129</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="O74" t="s" s="2">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10221,7 +10337,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10239,21 +10355,21 @@
         <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>21</v>
+        <v>425</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10273,18 +10389,20 @@
         <v>21</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>252</v>
+        <v>101</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -10333,7 +10451,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10348,24 +10466,24 @@
         <v>99</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>440</v>
+        <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>255</v>
+        <v>432</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10373,31 +10491,33 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>320</v>
+        <v>163</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
@@ -10445,7 +10565,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10460,24 +10580,24 @@
         <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>239</v>
+        <v>21</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>21</v>
+        <v>441</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10491,25 +10611,27 @@
         <v>87</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>102</v>
+        <v>444</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>103</v>
+        <v>445</v>
       </c>
       <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -10557,7 +10679,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>104</v>
+        <v>447</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10569,38 +10691,38 @@
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>105</v>
+        <v>448</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>21</v>
+        <v>449</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>21</v>
@@ -10609,21 +10731,23 @@
         <v>21</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>108</v>
+        <v>384</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>109</v>
+        <v>452</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>110</v>
+        <v>453</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
       </c>
@@ -10671,74 +10795,76 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>115</v>
+        <v>456</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>105</v>
+        <v>457</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>21</v>
+        <v>458</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C79" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="D79" t="s" s="2">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J79" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>329</v>
+        <v>254</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>330</v>
+        <v>255</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>111</v>
+        <v>256</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>331</v>
+        <v>257</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>21</v>
@@ -10763,13 +10889,11 @@
         <v>21</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>21</v>
+        <v>461</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>21</v>
@@ -10787,7 +10911,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>332</v>
+        <v>258</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10799,27 +10923,27 @@
         <v>21</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>188</v>
+        <v>259</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>449</v>
+        <v>414</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10845,10 +10969,10 @@
         <v>101</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>450</v>
+        <v>102</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>451</v>
+        <v>103</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -10899,7 +11023,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>449</v>
+        <v>104</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10911,38 +11035,38 @@
         <v>21</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>239</v>
+        <v>21</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>215</v>
+        <v>105</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>452</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>453</v>
+        <v>416</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>21</v>
@@ -10954,15 +11078,17 @@
         <v>21</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>454</v>
+        <v>108</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>455</v>
+        <v>109</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -10999,47 +11125,2893 @@
         <v>21</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF81" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AG81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
+      <c r="N86" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK81" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="AL81" t="s" s="2">
+      <c r="AK86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL86" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="AM81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN81" t="s" s="2">
+      <c r="AM86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>458</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="P87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="D90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="P104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>504</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN81">
+  <autoFilter ref="A1:AN106">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11049,7 +14021,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI80">
+  <conditionalFormatting sqref="A2:AI105">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3842" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3844" uniqueCount="505">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1097,7 +1097,7 @@
     <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet-elga-medikationmengenart</t>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-medikationmengenart</t>
   </si>
   <si>
     <t>Quantity.code</t>
@@ -1296,7 +1296,7 @@
     <t>Medication.ingredient.item[x].coding</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
+    <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
@@ -1306,9 +1306,6 @@
     <t>ATCWidO</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/AtElgaEmedValueSetATC</t>
-  </si>
-  <si>
     <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.id</t>
   </si>
   <si>
@@ -1339,6 +1336,9 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/atc-deutsch-wido</t>
+  </si>
+  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -1453,9 +1453,6 @@
     <t>WirkstoffeAges</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet/elga-wirkstoffe-ages</t>
-  </si>
-  <si>
     <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.id</t>
   </si>
   <si>
@@ -1463,6 +1460,9 @@
   </si>
   <si>
     <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.system</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/medikation-ages-wirkstoffe</t>
   </si>
   <si>
     <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.version</t>
@@ -9973,11 +9973,13 @@
         <v>21</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y71" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z71" t="s" s="2">
-        <v>412</v>
+        <v>21</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
@@ -10024,10 +10026,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10136,10 +10138,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10250,10 +10252,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10279,16 +10281,16 @@
         <v>129</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10298,7 +10300,7 @@
         <v>21</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>21</v>
+        <v>422</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>21</v>
@@ -10889,11 +10891,13 @@
         <v>21</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>461</v>
+        <v>21</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>21</v>
@@ -10940,10 +10944,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11052,10 +11056,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11166,10 +11170,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11195,16 +11199,16 @@
         <v>129</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -11214,7 +11218,7 @@
         <v>21</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>21</v>
+        <v>464</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -588,7 +588,7 @@
     <t>Medication.text.status</t>
   </si>
   <si>
-    <t>generated | extensions | additional | empty</t>
+    <t>Siehe Notes - "Regeln für den Inhalt der narrativen Teile in den Notes".</t>
   </si>
   <si>
     <t>The status of the narrative - whether it's entirely generated (from just the defined data or the extensions too), or whether a human authored it and it may contain additional data.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Bildet eine Magistrale Zubereitung in der "Medication"-Ressource ab. Wird grundsätzlich verwendet in Planeintrag, Geplanter Abgabe und Durchgeführter Abgabe.</t>
+    <t>Bildet eine Magistrale Zubereitung in der Medication-Ressource ab. Wird grundsätzlich verwendet in Planeintrag, Geplanter Abgabe und Durchgeführter Abgabe.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1537,7 +1537,7 @@
     <t>Medication.batch</t>
   </si>
   <si>
-    <t>Informationen zur Charge des Arzneimittels.</t>
+    <t>Details about packaged medications</t>
   </si>
   <si>
     <t>Information that only applies to packages (not products).</t>
@@ -13352,7 +13352,7 @@
         <v>78</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3844" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3841" uniqueCount="503">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1133,9 +1133,6 @@
     <t>Medication.amount.denominator.comparator</t>
   </si>
   <si>
-    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
-  </si>
-  <si>
     <t>Medication.amount.denominator.unit</t>
   </si>
   <si>
@@ -1177,6 +1174,366 @@
     <t>Medication.ingredient.modifierExtension</t>
   </si>
   <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]</t>
+  </si>
+  <si>
+    <t>The actual ingredient or content</t>
+  </si>
+  <si>
+    <t>The actual ingredient - either a substance (simple ingredient) or another medication of a medication.</t>
+  </si>
+  <si>
+    <t>The ingredient may reference a substance (for example, amoxicillin) or another medication (for example in the case of a compounded product, Glaxal Base).</t>
+  </si>
+  <si>
+    <t>.player</t>
+  </si>
+  <si>
+    <t>RXC-2-Component Code  if medication: RXO-1-Requested Give Code / RXE-2-Give Code / RXD-2-Dispense/Give Code / RXG-4-Give Code / RXA-5-Administered Code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.isActive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Active ingredient indicator</t>
+  </si>
+  <si>
+    <t>Indication of whether this ingredient affects the therapeutic action of the drug.</t>
+  </si>
+  <si>
+    <t>True indicates that the ingredient affects the therapeutic action of the drug (i.e. active). +False indicates that the ingredient does not affect the therapeutic action of the drug (i.e. inactive).</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.strength</t>
+  </si>
+  <si>
+    <t>Quantity of ingredient present</t>
+  </si>
+  <si>
+    <t>Specifies how many (or how much) of the items there are in this Medication.  For example, 250 mg per tablet.  This is expressed as a ratio where the numerator is 250mg and the denominator is 1 tablet.</t>
+  </si>
+  <si>
+    <t>//element(*,DrugCodedType)/Strength</t>
+  </si>
+  <si>
+    <t>RXC-3-Component Amount &amp; RXC-4-Component Units  if medication: RXO-2-Requested Give Amount - Minimum &amp; RXO-4-Requested Give Units / RXO-3-Requested Give Amount - Maximum &amp; RXO-4-Requested Give Units / RXO-11-Requested Dispense Amount &amp; RXO-12-Requested Dispense Units / RXE-3-Give Amount - Minimum &amp; RXE-5-Give Units / RXE-4-Give Amount - Maximum &amp; RXE-5-Give Units / RXE-10-Dispense Amount &amp; RXE-10-Dispense Units</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient</t>
+  </si>
+  <si>
+    <t>activeIngredient</t>
+  </si>
+  <si>
+    <t>Active or inactive ingredient</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.modifierExtension</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: Es sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x]</t>
+  </si>
+  <si>
+    <t>Inhaltsstoff codiert. Wirkstoff-Codes stammen aus der ATC-Klassifikation (Anatomical Therapeutic Chemical Classification), die von der WHO herausgegeben wird. Weitere Codes, wie auch die deutsche Bezeichnung der Codes, entsprechen dem GKV-Arzneimittelindex im Wissenschaftlichen Institut der AOK (WidO), AOK Bundesverband GbR, Deutschland, welcher auf den WHO ATC basiert. Zusätzlich kommen ergänzende Codes aus dem Arzneimittelverzeichnis der AGES zum Einsatz.</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO</t>
+  </si>
+  <si>
+    <t>ATCWidO</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.system</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/atc-deutsch-wido</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.version</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.display</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.userSelected</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges</t>
+  </si>
+  <si>
+    <t>WirkstoffeAges</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.system</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/medikation-ages-wirkstoffe</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.version</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.display</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.userSelected</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.item[x].text</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].text</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.isActive</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:activeIngredient.strength</t>
+  </si>
+  <si>
+    <t>Menge der vorhandenen Zutaten.</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient</t>
+  </si>
+  <si>
+    <t>inactiveIngredient</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.modifierExtension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.item[x]</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.item[x].id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.item[x].extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.item[x].coding</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.item[x].text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.isActive</t>
+  </si>
+  <si>
+    <t>Medication.ingredient:inactiveIngredient.strength</t>
+  </si>
+  <si>
+    <t>Medication.batch</t>
+  </si>
+  <si>
+    <t>Details about packaged medications</t>
+  </si>
+  <si>
+    <t>Information that only applies to packages (not products).</t>
+  </si>
+  <si>
+    <t>.player[classCode=CONT]</t>
+  </si>
+  <si>
+    <t>Medication.batch.id</t>
+  </si>
+  <si>
+    <t>Medication.batch.extension</t>
+  </si>
+  <si>
+    <t>Medication.batch.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user contentmodifiers</t>
   </si>
@@ -1189,370 +1546,6 @@
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]</t>
-  </si>
-  <si>
-    <t>CodeableConcept
-Reference(Substance|4.0.1|Medication|4.0.1)</t>
-  </si>
-  <si>
-    <t>The actual ingredient or content</t>
-  </si>
-  <si>
-    <t>The actual ingredient - either a substance (simple ingredient) or another medication of a medication.</t>
-  </si>
-  <si>
-    <t>The ingredient may reference a substance (for example, amoxicillin) or another medication (for example in the case of a compounded product, Glaxal Base).</t>
-  </si>
-  <si>
-    <t>.player</t>
-  </si>
-  <si>
-    <t>RXC-2-Component Code  if medication: RXO-1-Requested Give Code / RXE-2-Give Code / RXD-2-Dispense/Give Code / RXG-4-Give Code / RXA-5-Administered Code</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.isActive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>Active ingredient indicator</t>
-  </si>
-  <si>
-    <t>Indication of whether this ingredient affects the therapeutic action of the drug.</t>
-  </si>
-  <si>
-    <t>True indicates that the ingredient affects the therapeutic action of the drug (i.e. active). -False indicates that the ingredient does not affect the therapeutic action of the drug (i.e. inactive).</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.strength</t>
-  </si>
-  <si>
-    <t>Quantity of ingredient present</t>
-  </si>
-  <si>
-    <t>Specifies how many (or how much) of the items there are in this Medication.  For example, 250 mg per tablet.  This is expressed as a ratio where the numerator is 250mg and the denominator is 1 tablet.</t>
-  </si>
-  <si>
-    <t>//element(*,DrugCodedType)/Strength</t>
-  </si>
-  <si>
-    <t>RXC-3-Component Amount &amp; RXC-4-Component Units  if medication: RXO-2-Requested Give Amount - Minimum &amp; RXO-4-Requested Give Units / RXO-3-Requested Give Amount - Maximum &amp; RXO-4-Requested Give Units / RXO-11-Requested Dispense Amount &amp; RXO-12-Requested Dispense Units / RXE-3-Give Amount - Minimum &amp; RXE-5-Give Units / RXE-4-Give Amount - Maximum &amp; RXE-5-Give Units / RXE-10-Dispense Amount &amp; RXE-10-Dispense Units</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient</t>
-  </si>
-  <si>
-    <t>activeIngredient</t>
-  </si>
-  <si>
-    <t>Active or inactive ingredient</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.modifierExtension</t>
-  </si>
-  <si>
-    <t>Fachliche Begründung: Es sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x]</t>
-  </si>
-  <si>
-    <t>Inhaltsstoff codiert. Wirkstoff-Codes stammen aus der ATC-Klassifikation (Anatomical Therapeutic Chemical Classification), die von der WHO herausgegeben wird. Weitere Codes, wie auch die deutsche Bezeichnung der Codes, entsprechen dem GKV-Arzneimittelindex im Wissenschaftlichen Institut der AOK (WidO), AOK Bundesverband GbR, Deutschland, welcher auf den WHO ATC basiert. Zusätzlich kommen ergänzende Codes aus dem Arzneimittelverzeichnis der AGES zum Einsatz.</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].coding</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:system}
-</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO</t>
-  </si>
-  <si>
-    <t>ATCWidO</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.system</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>https://termgit.elga.gv.at/CodeSystem/atc-deutsch-wido</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.version</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.code</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.display</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.userSelected</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges</t>
-  </si>
-  <si>
-    <t>WirkstoffeAges</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.system</t>
-  </si>
-  <si>
-    <t>https://termgit.elga.gv.at/CodeSystem/medikation-ages-wirkstoffe</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.version</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.code</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.display</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges.userSelected</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.item[x].text</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].text</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.isActive</t>
-  </si>
-  <si>
-    <t>true</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:activeIngredient.strength</t>
-  </si>
-  <si>
-    <t>Menge der vorhandenen Zutaten.</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:inactiveIngredient</t>
-  </si>
-  <si>
-    <t>inactiveIngredient</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:inactiveIngredient.id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:inactiveIngredient.extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:inactiveIngredient.modifierExtension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:inactiveIngredient.item[x]</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:inactiveIngredient.item[x].id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:inactiveIngredient.item[x].extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:inactiveIngredient.item[x].coding</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:inactiveIngredient.item[x].text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:inactiveIngredient.isActive</t>
-  </si>
-  <si>
-    <t>Medication.ingredient:inactiveIngredient.strength</t>
-  </si>
-  <si>
-    <t>Medication.batch</t>
-  </si>
-  <si>
-    <t>Details about packaged medications</t>
-  </si>
-  <si>
-    <t>Information that only applies to packages (not products).</t>
-  </si>
-  <si>
-    <t>.player[classCode=CONT]</t>
-  </si>
-  <si>
-    <t>Medication.batch.id</t>
-  </si>
-  <si>
-    <t>Medication.batch.extension</t>
-  </si>
-  <si>
-    <t>Medication.batch.modifierExtension</t>
   </si>
   <si>
     <t>Medication.batch.lotNumber</t>
@@ -4243,7 +4236,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
@@ -4355,7 +4348,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>87</v>
@@ -4678,7 +4671,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>217</v>
       </c>
@@ -4697,7 +4690,7 @@
         <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>21</v>
@@ -5143,7 +5136,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>87</v>
@@ -6716,7 +6709,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>307</v>
       </c>
@@ -6729,13 +6722,13 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -6948,7 +6941,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>326</v>
       </c>
@@ -6967,7 +6960,7 @@
         <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
@@ -7290,7 +7283,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>348</v>
       </c>
@@ -7303,13 +7296,13 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
@@ -7628,7 +7621,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>355</v>
       </c>
@@ -7641,13 +7634,13 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
@@ -7678,7 +7671,7 @@
         <v>21</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>21</v>
@@ -7760,7 +7753,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -7775,7 +7768,7 @@
         <v>163</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="M52" t="s" s="2">
         <v>318</v>
@@ -7860,12 +7853,12 @@
         <v>325</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7876,10 +7869,10 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>21</v>
@@ -7976,10 +7969,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8088,12 +8081,12 @@
         <v>332</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8104,10 +8097,10 @@
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
@@ -8153,13 +8146,11 @@
         <v>21</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>21</v>
@@ -8206,10 +8197,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8232,16 +8223,16 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8279,7 +8270,7 @@
         <v>21</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AC56" s="2"/>
       <c r="AD56" t="s" s="2">
@@ -8289,7 +8280,7 @@
         <v>114</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8307,7 +8298,7 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>21</v>
@@ -8318,10 +8309,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8430,10 +8421,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8544,21 +8535,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>371</v>
+        <v>21</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -8573,17 +8564,13 @@
         <v>108</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>372</v>
+        <v>231</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8631,7 +8618,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8649,7 +8636,7 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
@@ -8658,12 +8645,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8677,7 +8664,7 @@
         <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>21</v>
@@ -8686,17 +8673,17 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>377</v>
+        <v>241</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -8745,7 +8732,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>87</v>
@@ -8763,21 +8750,21 @@
         <v>247</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8800,17 +8787,17 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -8859,7 +8846,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8877,7 +8864,7 @@
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
@@ -8888,10 +8875,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8917,10 +8904,10 @@
         <v>293</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8971,7 +8958,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8986,7 +8973,7 @@
         <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>296</v>
@@ -8995,18 +8982,18 @@
         <v>21</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>21</v>
@@ -9028,16 +9015,16 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="M63" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9087,7 +9074,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9105,7 +9092,7 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>21</v>
@@ -9116,10 +9103,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9228,10 +9215,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9342,10 +9329,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9371,7 +9358,7 @@
         <v>108</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="M66" t="s" s="2">
         <v>205</v>
@@ -9425,7 +9412,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9454,10 +9441,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9483,14 +9470,14 @@
         <v>241</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -9539,7 +9526,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>87</v>
@@ -9557,21 +9544,21 @@
         <v>247</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9680,10 +9667,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9794,10 +9781,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9869,7 +9856,7 @@
         <v>21</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="AC70" s="2"/>
       <c r="AD70" t="s" s="2">
@@ -9908,13 +9895,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>21</v>
@@ -10026,10 +10013,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10138,10 +10125,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10252,10 +10239,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10281,16 +10268,16 @@
         <v>129</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10300,7 +10287,7 @@
         <v>21</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>21</v>
@@ -10339,7 +10326,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10357,21 +10344,21 @@
         <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10397,13 +10384,13 @@
         <v>101</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10453,7 +10440,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10471,21 +10458,21 @@
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10511,14 +10498,14 @@
         <v>163</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
@@ -10567,7 +10554,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10585,21 +10572,21 @@
         <v>21</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10625,14 +10612,14 @@
         <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
@@ -10681,7 +10668,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10699,21 +10686,21 @@
         <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>449</v>
+        <v>443</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10736,19 +10723,19 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -10797,7 +10784,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10815,24 +10802,24 @@
         <v>21</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>21</v>
@@ -10944,10 +10931,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11056,10 +11043,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11170,10 +11157,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11199,16 +11186,16 @@
         <v>129</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -11218,7 +11205,7 @@
         <v>21</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>21</v>
@@ -11257,7 +11244,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11275,21 +11262,21 @@
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11315,13 +11302,13 @@
         <v>101</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11371,7 +11358,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11389,21 +11376,21 @@
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11429,14 +11416,14 @@
         <v>163</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -11485,7 +11472,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11503,21 +11490,21 @@
         <v>21</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11543,14 +11530,14 @@
         <v>101</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
@@ -11599,7 +11586,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11617,21 +11604,21 @@
         <v>21</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>449</v>
+        <v>443</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11654,19 +11641,19 @@
         <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>21</v>
@@ -11715,7 +11702,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11733,21 +11720,21 @@
         <v>21</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11860,10 +11847,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11886,17 +11873,17 @@
         <v>21</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>21</v>
@@ -11906,7 +11893,7 @@
         <v>21</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>21</v>
@@ -11945,7 +11932,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -11963,7 +11950,7 @@
         <v>21</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>21</v>
@@ -11974,10 +11961,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12003,10 +11990,10 @@
         <v>293</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12057,7 +12044,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12072,7 +12059,7 @@
         <v>99</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>296</v>
@@ -12081,18 +12068,18 @@
         <v>21</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>21</v>
@@ -12114,16 +12101,16 @@
         <v>21</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="M90" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12173,7 +12160,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12191,7 +12178,7 @@
         <v>21</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>21</v>
@@ -12202,10 +12189,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12314,10 +12301,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12428,10 +12415,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12457,7 +12444,7 @@
         <v>108</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="M93" t="s" s="2">
         <v>205</v>
@@ -12511,7 +12498,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12540,10 +12527,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12569,14 +12556,14 @@
         <v>241</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>21</v>
@@ -12625,7 +12612,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>87</v>
@@ -12643,21 +12630,21 @@
         <v>247</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12766,10 +12753,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12880,10 +12867,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12996,10 +12983,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13025,7 +13012,7 @@
         <v>101</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="M98" t="s" s="2">
         <v>263</v>
@@ -13112,10 +13099,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13138,17 +13125,17 @@
         <v>21</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>21</v>
@@ -13197,7 +13184,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13215,7 +13202,7 @@
         <v>21</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>21</v>
@@ -13226,10 +13213,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13255,10 +13242,10 @@
         <v>293</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13309,7 +13296,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13324,7 +13311,7 @@
         <v>99</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>296</v>
@@ -13333,15 +13320,15 @@
         <v>21</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13364,13 +13351,13 @@
         <v>21</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13421,7 +13408,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13439,7 +13426,7 @@
         <v>280</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>21</v>
@@ -13450,10 +13437,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13562,10 +13549,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13676,14 +13663,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>371</v>
+        <v>489</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -13705,16 +13692,16 @@
         <v>108</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>372</v>
+        <v>490</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>373</v>
+        <v>491</v>
       </c>
       <c r="N104" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>374</v>
+        <v>492</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>21</v>
@@ -13763,7 +13750,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -13792,10 +13779,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13821,10 +13808,10 @@
         <v>101</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13875,7 +13862,7 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -13899,15 +13886,15 @@
         <v>21</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13930,13 +13917,13 @@
         <v>21</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -13987,7 +13974,7 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14005,13 +13992,13 @@
         <v>280</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$117</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3841" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4239" uniqueCount="514">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -934,6 +934,142 @@
     <t>RXO-5-Requested Dosage Form / RXE-6-Give Dosage Form / RXD-6-Actual Dosage Form / RXG-8-Give Dosage Form / RXA-8-Administered Dosage Form</t>
   </si>
   <si>
+    <t>Medication.form.id</t>
+  </si>
+  <si>
+    <t>Medication.form.extension</t>
+  </si>
+  <si>
+    <t>Medication.form.coding</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.id</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.extension</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Medication.form.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>Medication.form.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
     <t>Medication.amount</t>
   </si>
   <si>
@@ -1198,10 +1334,6 @@
     <t>Medication.ingredient.isActive</t>
   </si>
   <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
     <t>Active ingredient indicator</t>
   </si>
   <si>
@@ -1303,129 +1435,33 @@
     <t>Medication.ingredient.item[x].coding.system</t>
   </si>
   <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
     <t>https://termgit.elga.gv.at/CodeSystem/atc-deutsch-wido</t>
   </si>
   <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
     <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.version</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding.version</t>
   </si>
   <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
     <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.code</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding.code</t>
   </si>
   <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
     <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.display</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding.display</t>
   </si>
   <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
     <t>Medication.ingredient:activeIngredient.item[x].coding:ATCWidO.userSelected</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x].coding.userSelected</t>
   </si>
   <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
     <t>Medication.ingredient:activeIngredient.item[x].coding:WirkstoffeAges</t>
   </si>
   <si>
@@ -1502,9 +1538,6 @@
   </si>
   <si>
     <t>Medication.ingredient:inactiveIngredient.item[x].text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
   </si>
   <si>
     <t>Medication.ingredient:inactiveIngredient.isActive</t>
@@ -1901,7 +1934,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN106"/>
+  <dimension ref="A1:AN117"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="66.546875" customWidth="true" bestFit="true"/>
@@ -4242,7 +4275,7 @@
         <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>21</v>
@@ -6033,7 +6066,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>292</v>
       </c>
@@ -6052,22 +6085,22 @@
         <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>293</v>
+        <v>101</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>294</v>
+        <v>102</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>295</v>
+        <v>103</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6118,7 +6151,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>292</v>
+        <v>104</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6130,13 +6163,13 @@
         <v>21</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>296</v>
+        <v>105</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
@@ -6147,21 +6180,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>21</v>
@@ -6173,15 +6206,17 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6218,31 +6253,31 @@
         <v>21</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>21</v>
@@ -6257,46 +6292,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>109</v>
+        <v>254</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>110</v>
+        <v>255</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6332,19 +6369,19 @@
         <v>21</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>115</v>
+        <v>258</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6356,27 +6393,27 @@
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6384,28 +6421,28 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>300</v>
+        <v>101</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>301</v>
+        <v>102</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>302</v>
+        <v>103</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6456,7 +6493,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>303</v>
+        <v>104</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6468,13 +6505,13 @@
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>304</v>
+        <v>105</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
@@ -6485,21 +6522,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6511,15 +6548,17 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6556,31 +6595,31 @@
         <v>21</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
@@ -6595,46 +6634,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>109</v>
+        <v>298</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>110</v>
+        <v>299</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6670,51 +6711,51 @@
         <v>21</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>115</v>
+        <v>302</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>105</v>
+        <v>303</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>21</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6722,7 +6763,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>87</v>
@@ -6737,20 +6778,18 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="L43" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>312</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6798,7 +6837,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6816,21 +6855,21 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6838,16 +6877,16 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>88</v>
@@ -6856,21 +6895,19 @@
         <v>163</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q44" t="s" s="2">
-        <v>320</v>
-      </c>
+      <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6890,13 +6927,13 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>321</v>
+        <v>21</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>322</v>
+        <v>21</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -6914,7 +6951,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6932,21 +6969,21 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6972,14 +7009,14 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7028,7 +7065,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7046,21 +7083,21 @@
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7083,17 +7120,19 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>129</v>
+        <v>327</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="O46" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7142,7 +7181,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7151,7 +7190,7 @@
         <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>338</v>
+        <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>99</v>
@@ -7160,21 +7199,21 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7182,13 +7221,13 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>21</v>
@@ -7197,19 +7236,19 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>163</v>
+        <v>101</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>342</v>
+        <v>263</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>343</v>
+        <v>264</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>344</v>
+        <v>265</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7234,11 +7273,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y47" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z47" t="s" s="2">
-        <v>345</v>
+        <v>21</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7256,7 +7297,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>346</v>
+        <v>266</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7274,21 +7315,21 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>347</v>
+        <v>267</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>332</v>
+        <v>268</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7296,7 +7337,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>87</v>
@@ -7311,13 +7352,13 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>300</v>
+        <v>338</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7368,7 +7409,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7386,7 +7427,7 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
@@ -7397,10 +7438,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7509,10 +7550,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7623,10 +7664,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7649,20 +7690,16 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>308</v>
+        <v>345</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
       </c>
@@ -7710,7 +7747,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>313</v>
+        <v>348</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7728,21 +7765,21 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>314</v>
+        <v>349</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>315</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7753,36 +7790,32 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>163</v>
+        <v>101</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>317</v>
+        <v>102</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>318</v>
+        <v>103</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>319</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q52" t="s" s="2">
-        <v>320</v>
-      </c>
+      <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
         <v>21</v>
       </c>
@@ -7802,13 +7835,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>321</v>
+        <v>21</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>322</v>
+        <v>21</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -7826,7 +7859,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>323</v>
+        <v>104</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7838,61 +7871,61 @@
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>324</v>
+        <v>105</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>325</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>327</v>
+        <v>109</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -7928,51 +7961,51 @@
         <v>21</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>330</v>
+        <v>115</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>331</v>
+        <v>105</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>332</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7980,13 +8013,13 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
@@ -7995,17 +8028,19 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>129</v>
+        <v>353</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8054,7 +8089,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8063,7 +8098,7 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>338</v>
+        <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>99</v>
@@ -8072,21 +8107,21 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>332</v>
+        <v>360</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8097,13 +8132,13 @@
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I55" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>88</v>
@@ -8112,21 +8147,21 @@
         <v>163</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q55" s="2"/>
+      <c r="Q55" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="R55" t="s" s="2">
         <v>21</v>
       </c>
@@ -8148,9 +8183,11 @@
       <c r="X55" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Y55" s="2"/>
+      <c r="Y55" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="Z55" t="s" s="2">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>21</v>
@@ -8168,7 +8205,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8186,21 +8223,21 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>332</v>
+        <v>370</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8208,10 +8245,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>88</v>
@@ -8220,21 +8257,21 @@
         <v>21</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>361</v>
+        <v>101</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8270,23 +8307,25 @@
         <v>21</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AC56" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
@@ -8298,21 +8337,21 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>21</v>
+        <v>377</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8332,19 +8371,21 @@
         <v>21</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>102</v>
+        <v>379</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>103</v>
+        <v>380</v>
       </c>
       <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8392,7 +8433,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>104</v>
+        <v>382</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8401,64 +8442,66 @@
         <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>21</v>
+        <v>383</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>105</v>
+        <v>384</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>21</v>
+        <v>377</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>109</v>
+        <v>386</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>110</v>
+        <v>387</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8482,13 +8525,11 @@
         <v>21</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>21</v>
+        <v>390</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>21</v>
@@ -8506,39 +8547,39 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>115</v>
+        <v>391</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>105</v>
+        <v>392</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>21</v>
+        <v>377</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8546,28 +8587,28 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>108</v>
+        <v>345</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>231</v>
+        <v>394</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>205</v>
+        <v>395</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8618,25 +8659,25 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>21</v>
+        <v>397</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
@@ -8645,12 +8686,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8658,13 +8699,13 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>21</v>
@@ -8673,18 +8714,16 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>241</v>
+        <v>101</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>372</v>
+        <v>102</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>373</v>
+        <v>103</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>374</v>
-      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -8732,10 +8771,10 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>371</v>
+        <v>104</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>87</v>
@@ -8744,38 +8783,38 @@
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>247</v>
+        <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>375</v>
+        <v>105</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>376</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -8787,18 +8826,18 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>378</v>
+        <v>108</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>379</v>
+        <v>109</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -8834,37 +8873,37 @@
         <v>21</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>377</v>
+        <v>115</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>382</v>
+        <v>105</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
@@ -8873,12 +8912,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8886,31 +8925,35 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>293</v>
+        <v>353</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>384</v>
+        <v>354</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -8958,7 +9001,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8973,28 +9016,26 @@
         <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>386</v>
+        <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>296</v>
+        <v>359</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>387</v>
+        <v>360</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>389</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>21</v>
       </c>
@@ -9003,34 +9044,36 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I63" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I63" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J63" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>361</v>
+        <v>163</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>390</v>
+        <v>362</v>
       </c>
       <c r="M63" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q63" s="2"/>
+      <c r="Q63" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="R63" t="s" s="2">
         <v>21</v>
       </c>
@@ -9050,13 +9093,13 @@
         <v>21</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>21</v>
+        <v>366</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>21</v>
+        <v>367</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -9074,13 +9117,13 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
@@ -9092,21 +9135,21 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>21</v>
+        <v>370</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>367</v>
+        <v>402</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9120,25 +9163,27 @@
         <v>87</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>102</v>
+        <v>372</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>103</v>
+        <v>373</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
@@ -9186,7 +9231,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>104</v>
+        <v>375</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9198,38 +9243,38 @@
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>105</v>
+        <v>376</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>21</v>
+        <v>377</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>368</v>
+        <v>403</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -9238,21 +9283,21 @@
         <v>21</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>109</v>
+        <v>379</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9300,39 +9345,39 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>115</v>
+        <v>382</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>21</v>
+        <v>383</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>105</v>
+        <v>384</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>21</v>
+        <v>377</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>369</v>
+        <v>404</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9343,28 +9388,32 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9388,13 +9437,11 @@
         <v>21</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>21</v>
+        <v>390</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -9412,39 +9459,39 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>21</v>
+        <v>377</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9455,7 +9502,7 @@
         <v>87</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>88</v>
@@ -9467,18 +9514,18 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>241</v>
+        <v>406</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -9514,25 +9561,23 @@
         <v>21</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="AC67" s="2"/>
       <c r="AD67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
@@ -9541,24 +9586,24 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>247</v>
+        <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>375</v>
+        <v>411</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>376</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9667,10 +9712,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9740,16 +9785,16 @@
         <v>21</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>115</v>
@@ -9781,10 +9826,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9792,35 +9837,31 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I70" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J70" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
       </c>
@@ -9856,17 +9897,19 @@
         <v>21</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AC70" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>258</v>
+        <v>415</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9878,37 +9921,35 @@
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>259</v>
+        <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>260</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>87</v>
@@ -9920,22 +9961,20 @@
         <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>141</v>
+        <v>241</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>254</v>
+        <v>417</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>257</v>
+        <v>419</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -9984,13 +10023,13 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>258</v>
+        <v>416</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
@@ -9999,24 +10038,24 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>259</v>
+        <v>420</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>260</v>
+        <v>421</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10039,16 +10078,18 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>101</v>
+        <v>327</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>102</v>
+        <v>423</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>103</v>
+        <v>424</v>
       </c>
       <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+      <c r="O72" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>21</v>
       </c>
@@ -10096,7 +10137,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>104</v>
+        <v>422</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10108,13 +10149,13 @@
         <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>105</v>
+        <v>426</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>21</v>
@@ -10125,21 +10166,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>21</v>
@@ -10151,17 +10192,15 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>108</v>
+        <v>338</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>109</v>
+        <v>428</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -10198,62 +10237,64 @@
         <v>21</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>115</v>
+        <v>427</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>21</v>
+        <v>430</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>105</v>
+        <v>341</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>21</v>
+        <v>431</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C74" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="D74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>88</v>
@@ -10262,23 +10303,21 @@
         <v>21</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>129</v>
+        <v>406</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>21</v>
       </c>
@@ -10287,7 +10326,7 @@
         <v>21</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>416</v>
+        <v>21</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>21</v>
@@ -10326,13 +10365,13 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>21</v>
@@ -10344,21 +10383,21 @@
         <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>419</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10372,26 +10411,24 @@
         <v>87</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>422</v>
+        <v>102</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -10440,7 +10477,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>425</v>
+        <v>104</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10452,61 +10489,61 @@
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>426</v>
+        <v>105</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>427</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>430</v>
+        <v>109</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
@@ -10554,39 +10591,39 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>433</v>
+        <v>115</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>434</v>
+        <v>105</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>435</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>437</v>
+        <v>414</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10597,30 +10634,28 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I77" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>438</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>439</v>
+        <v>205</v>
       </c>
       <c r="N77" s="2"/>
-      <c r="O77" t="s" s="2">
-        <v>440</v>
-      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -10668,39 +10703,39 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>442</v>
+        <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>443</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>445</v>
+        <v>416</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10708,34 +10743,32 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>378</v>
+        <v>241</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>449</v>
+        <v>419</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -10784,10 +10817,10 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>450</v>
+        <v>416</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>87</v>
@@ -10799,28 +10832,26 @@
         <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>451</v>
+        <v>420</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>452</v>
+        <v>421</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>21</v>
       </c>
@@ -10832,29 +10863,25 @@
         <v>87</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>254</v>
+        <v>102</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>21</v>
       </c>
@@ -10902,50 +10929,50 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>258</v>
+        <v>104</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>259</v>
+        <v>105</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>260</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>407</v>
+        <v>444</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>21</v>
@@ -10957,15 +10984,17 @@
         <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -11002,31 +11031,31 @@
         <v>21</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>21</v>
@@ -11043,44 +11072,46 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>109</v>
+        <v>254</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>110</v>
+        <v>255</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>21</v>
       </c>
@@ -11116,11 +11147,9 @@
         <v>21</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="AC81" s="2"/>
       <c r="AD81" t="s" s="2">
         <v>21</v>
       </c>
@@ -11128,7 +11157,7 @@
         <v>114</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>115</v>
+        <v>258</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11140,35 +11169,37 @@
         <v>21</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C82" s="2"/>
+        <v>446</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="D82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>87</v>
@@ -11183,19 +11214,19 @@
         <v>88</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>412</v>
+        <v>254</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>413</v>
+        <v>255</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>414</v>
+        <v>256</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>415</v>
+        <v>257</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -11205,7 +11236,7 @@
         <v>21</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>458</v>
+        <v>21</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>21</v>
@@ -11244,13 +11275,13 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>417</v>
+        <v>258</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>21</v>
@@ -11262,21 +11293,21 @@
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>418</v>
+        <v>259</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>419</v>
+        <v>260</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11290,26 +11321,24 @@
         <v>87</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>422</v>
+        <v>102</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -11358,7 +11387,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>425</v>
+        <v>104</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11370,61 +11399,61 @@
         <v>21</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>426</v>
+        <v>105</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>427</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>430</v>
+        <v>109</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
@@ -11460,51 +11489,51 @@
         <v>21</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>433</v>
+        <v>115</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>434</v>
+        <v>105</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>435</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11512,7 +11541,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>87</v>
@@ -11527,17 +11556,19 @@
         <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>438</v>
+        <v>298</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="O85" t="s" s="2">
-        <v>440</v>
+        <v>301</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
@@ -11547,7 +11578,7 @@
         <v>21</v>
       </c>
       <c r="S85" t="s" s="2">
-        <v>21</v>
+        <v>456</v>
       </c>
       <c r="T85" t="s" s="2">
         <v>21</v>
@@ -11586,7 +11617,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>441</v>
+        <v>302</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11604,21 +11635,21 @@
         <v>21</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>442</v>
+        <v>303</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>443</v>
+        <v>304</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11632,7 +11663,7 @@
         <v>87</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>21</v>
@@ -11641,20 +11672,18 @@
         <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>378</v>
+        <v>101</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>446</v>
+        <v>306</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>447</v>
+        <v>307</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>21</v>
       </c>
@@ -11702,7 +11731,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>450</v>
+        <v>309</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11720,21 +11749,21 @@
         <v>21</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>451</v>
+        <v>310</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>452</v>
+        <v>311</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11742,13 +11771,13 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>21</v>
@@ -11757,19 +11786,17 @@
         <v>88</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>265</v>
+        <v>315</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>21</v>
@@ -11818,7 +11845,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>266</v>
+        <v>316</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11836,21 +11863,21 @@
         <v>21</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>267</v>
+        <v>317</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>268</v>
+        <v>318</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>377</v>
+        <v>462</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11858,7 +11885,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>87</v>
@@ -11870,20 +11897,20 @@
         <v>21</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>378</v>
+        <v>101</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>379</v>
+        <v>320</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>380</v>
+        <v>321</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>381</v>
+        <v>322</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>21</v>
@@ -11893,7 +11920,7 @@
         <v>21</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>466</v>
+        <v>21</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>21</v>
@@ -11932,7 +11959,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>377</v>
+        <v>323</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -11950,21 +11977,21 @@
         <v>21</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>382</v>
+        <v>324</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>21</v>
+        <v>325</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>383</v>
+        <v>464</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11978,25 +12005,29 @@
         <v>87</v>
       </c>
       <c r="H89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J89" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K89" t="s" s="2">
-        <v>293</v>
+        <v>327</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>468</v>
+        <v>328</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>21</v>
       </c>
@@ -12044,7 +12075,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>383</v>
+        <v>332</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12059,27 +12090,27 @@
         <v>99</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>386</v>
+        <v>21</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>296</v>
+        <v>333</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>387</v>
+        <v>334</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>360</v>
+        <v>446</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>21</v>
@@ -12089,7 +12120,7 @@
         <v>78</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>88</v>
@@ -12098,21 +12129,23 @@
         <v>21</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>361</v>
+        <v>141</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>390</v>
+        <v>254</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>363</v>
+        <v>255</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
       </c>
@@ -12160,7 +12193,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>360</v>
+        <v>258</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12178,21 +12211,21 @@
         <v>21</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>366</v>
+        <v>259</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>367</v>
+        <v>451</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12301,10 +12334,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>368</v>
+        <v>453</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12374,16 +12407,16 @@
         <v>21</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF92" t="s" s="2">
         <v>115</v>
@@ -12413,12 +12446,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>369</v>
+        <v>455</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12426,31 +12459,35 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J93" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>394</v>
+        <v>298</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>21</v>
       </c>
@@ -12459,7 +12496,7 @@
         <v>21</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>21</v>
+        <v>470</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>21</v>
@@ -12498,39 +12535,39 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>370</v>
+        <v>302</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>21</v>
+        <v>303</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>21</v>
+        <v>304</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>371</v>
+        <v>458</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12538,7 +12575,7 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>87</v>
@@ -12550,21 +12587,21 @@
         <v>21</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>241</v>
+        <v>101</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>372</v>
+        <v>306</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>21</v>
       </c>
@@ -12612,10 +12649,10 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>371</v>
+        <v>309</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>87</v>
@@ -12627,24 +12664,24 @@
         <v>99</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>247</v>
+        <v>21</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>375</v>
+        <v>310</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>376</v>
+        <v>311</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>398</v>
+        <v>460</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12652,31 +12689,33 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>102</v>
+        <v>313</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>103</v>
+        <v>314</v>
       </c>
       <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>21</v>
       </c>
@@ -12724,7 +12763,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>104</v>
+        <v>316</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -12736,61 +12775,61 @@
         <v>21</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>105</v>
+        <v>317</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>21</v>
+        <v>318</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>400</v>
+        <v>462</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>109</v>
+        <v>320</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>21</v>
       </c>
@@ -12826,51 +12865,51 @@
         <v>21</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>115</v>
+        <v>323</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>105</v>
+        <v>324</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>21</v>
+        <v>325</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>402</v>
+        <v>464</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12881,7 +12920,7 @@
         <v>78</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>21</v>
@@ -12893,19 +12932,19 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>141</v>
+        <v>327</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>254</v>
+        <v>328</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>255</v>
+        <v>329</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>256</v>
+        <v>330</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>257</v>
+        <v>331</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>21</v>
@@ -12954,13 +12993,13 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>258</v>
+        <v>332</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>21</v>
@@ -12972,21 +13011,21 @@
         <v>21</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>259</v>
+        <v>333</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>260</v>
+        <v>334</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12997,10 +13036,10 @@
         <v>78</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>21</v>
@@ -13012,7 +13051,7 @@
         <v>101</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>479</v>
+        <v>362</v>
       </c>
       <c r="M98" t="s" s="2">
         <v>263</v>
@@ -13099,10 +13138,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>377</v>
+        <v>422</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13125,17 +13164,17 @@
         <v>21</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>378</v>
+        <v>327</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>379</v>
+        <v>423</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>380</v>
+        <v>424</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>381</v>
+        <v>425</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>21</v>
@@ -13145,7 +13184,7 @@
         <v>21</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>35</v>
+        <v>478</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>21</v>
@@ -13184,7 +13223,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>377</v>
+        <v>422</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13202,7 +13241,7 @@
         <v>21</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>382</v>
+        <v>426</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>21</v>
@@ -13213,10 +13252,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>383</v>
+        <v>427</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13239,13 +13278,13 @@
         <v>21</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>385</v>
+        <v>429</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13296,7 +13335,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>383</v>
+        <v>427</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13311,26 +13350,28 @@
         <v>99</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>386</v>
+        <v>430</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>296</v>
+        <v>341</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>387</v>
+        <v>431</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C101" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="B101" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>21</v>
       </c>
@@ -13339,10 +13380,10 @@
         <v>78</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>21</v>
@@ -13351,15 +13392,17 @@
         <v>21</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>361</v>
+        <v>406</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>483</v>
+        <v>434</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>21</v>
@@ -13408,13 +13451,13 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>482</v>
+        <v>405</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>21</v>
@@ -13423,10 +13466,10 @@
         <v>99</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>280</v>
+        <v>21</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>485</v>
+        <v>411</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>21</v>
@@ -13437,10 +13480,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>486</v>
+        <v>412</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13549,10 +13592,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>487</v>
+        <v>413</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13663,21 +13706,21 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>488</v>
+        <v>414</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>489</v>
+        <v>21</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>21</v>
@@ -13692,17 +13735,13 @@
         <v>108</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>490</v>
+        <v>438</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>21</v>
       </c>
@@ -13750,7 +13789,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>370</v>
+        <v>415</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -13768,7 +13807,7 @@
         <v>21</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>21</v>
@@ -13777,12 +13816,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>493</v>
+        <v>416</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13790,13 +13829,13 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G105" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>21</v>
@@ -13805,16 +13844,18 @@
         <v>21</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>101</v>
+        <v>241</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>494</v>
+        <v>417</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>495</v>
+        <v>418</v>
       </c>
       <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
+      <c r="O105" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>21</v>
       </c>
@@ -13862,10 +13903,10 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>493</v>
+        <v>416</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>87</v>
@@ -13877,24 +13918,24 @@
         <v>99</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>280</v>
+        <v>247</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>238</v>
+        <v>420</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>496</v>
+        <v>421</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>497</v>
+        <v>442</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13917,13 +13958,13 @@
         <v>21</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>498</v>
+        <v>101</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>499</v>
+        <v>102</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>500</v>
+        <v>103</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -13974,35 +14015,1285 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="P108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
+      <c r="P111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
+      <c r="P112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AG106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
+      <c r="B113" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="P115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK106" t="s" s="2">
+      <c r="AK116" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AL106" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>502</v>
+      <c r="AL116" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>513</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN106">
+  <autoFilter ref="A1:AN117">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14012,7 +15303,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI105">
+  <conditionalFormatting sqref="A2:AI116">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1148,7 +1148,7 @@
     <t>Medication.amount.numerator.comparator</t>
   </si>
   <si>
-    <t>Fachliche Begründung: TODO</t>
+    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
   </si>
   <si>
     <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
@@ -13051,7 +13051,7 @@
         <v>101</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>362</v>
+        <v>336</v>
       </c>
       <c r="M98" t="s" s="2">
         <v>263</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-magistrale-zubereitung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
